--- a/data/Overall Collection Summary - June 2026.xlsx
+++ b/data/Overall Collection Summary - June 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://raghavgroup.sharepoint.com/sites/CRM/Shared Documents/General/LAKSHYA TRACKERS MONTHLY/LAKSHYA CRM TRACKER/LAKSHYA CRM Tracker - June'26/Overall Summary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10317" documentId="8_{AED7C0B6-5B33-4314-A282-567B12F8F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5309017-817F-465A-AD96-6C6EE874D4E7}"/>
+  <xr:revisionPtr revIDLastSave="10342" documentId="8_{AED7C0B6-5B33-4314-A282-567B12F8F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24FC90DF-7D50-48C1-A65B-19765C6D2FC4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="917" firstSheet="2" activeTab="2" xr2:uid="{3D2F352B-9E05-401C-B527-666CFC22F994}"/>
   </bookViews>
@@ -2453,15 +2453,6 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2475,6 +2466,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3155,25 +3155,25 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1.0896982</c:v>
+                  <c:v>0.98969820000000008</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.29264247619047618</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9575439714285716</c:v>
+                  <c:v>2.148404561904762</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.6680721952380955</c:v>
+                  <c:v>2.756608838095238</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.1329154857142862</c:v>
+                  <c:v>5.137677390476191</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.6634805666666672</c:v>
+                  <c:v>5.8150255190476194</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3476,25 +3476,25 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="7"/>
                       <c:pt idx="0">
-                        <c:v>0.37316170811432692</c:v>
+                        <c:v>0.33891720737877218</c:v>
                       </c:pt>
                       <c:pt idx="1">
                         <c:v>9.3251272288981724E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.36850355234688975</c:v>
+                        <c:v>0.4044326587271535</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.32150794076471628</c:v>
+                        <c:v>0.33217678015295515</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.79932689831846071</c:v>
+                        <c:v>0.8000684493091238</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0.6299701886501804</c:v>
+                        <c:v>0.64682710218888106</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -3523,7 +3523,7 @@
                           <c:extLst>
                             <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                              <c16:uniqueId val="{00000002-C66E-46DA-A76B-11FAFD59EBF0}"/>
+                              <c16:uniqueId val="{00000002-8577-49EE-B700-0CF398B37908}"/>
                             </c:ext>
                           </c:extLst>
                         </c15:dLbl>
@@ -4257,22 +4257,22 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.4377010095238099</c:v>
+                  <c:v>4.6690129904761903</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.4396125714285715</c:v>
+                  <c:v>2.3747605714285718</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.3154152380952382</c:v>
+                  <c:v>1.3182723809523809</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.1081906857142858</c:v>
+                  <c:v>4.1224764</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.2899397714285707</c:v>
+                  <c:v>3.4306124523809518</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.5289088571428571</c:v>
+                  <c:v>2.5431945714285713</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4438,22 +4438,22 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="6"/>
                       <c:pt idx="0">
-                        <c:v>0.38303105484821071</c:v>
+                        <c:v>0.40299627374715741</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>2.6872072821538473</c:v>
+                        <c:v>2.6157734943863935</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>1.019701734957549</c:v>
+                        <c:v>1.0219165743816905</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.96500494617582055</c:v>
+                        <c:v>0.9683606290055653</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.34740652285412571</c:v>
+                        <c:v>0.36226108261678475</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0.27820779506522081</c:v>
+                        <c:v>0.27977938079522235</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7064,25 +7064,25 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.68969819999999993</c:v>
+                  <c:v>0.58969820000000006</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.29264247619047618</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.8337344476190478</c:v>
+                  <c:v>1.9769759904761905</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.2993296238095242</c:v>
+                  <c:v>2.5050992190476191</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>4.1363054857142858</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.31797660000000005</c:v>
+                  <c:v>0.3345262</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.1130300904761912</c:v>
+                  <c:v>5.2645750428571434</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7385,25 +7385,25 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="7"/>
                       <c:pt idx="0">
-                        <c:v>0.23618370517210788</c:v>
+                        <c:v>0.20193920443655317</c:v>
                       </c:pt>
                       <c:pt idx="1">
                         <c:v>9.4400798771121341E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.34754335371103784</c:v>
+                        <c:v>0.37469158461216606</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.28572075388021251</c:v>
+                        <c:v>0.31129022563765768</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0.68704711943287278</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0.16932480917207343</c:v>
+                        <c:v>0.17813758930078144</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0.6299701886501804</c:v>
+                        <c:v>0.64682710218888106</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7432,7 +7432,7 @@
                           <c:extLst>
                             <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                              <c16:uniqueId val="{00000002-6C2C-4678-8CCB-74EEB708069F}"/>
+                              <c16:uniqueId val="{00000002-DFEF-4440-B9D8-A914BD041D6F}"/>
                             </c:ext>
                           </c:extLst>
                         </c15:dLbl>
@@ -8234,22 +8234,22 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.4410592095238099</c:v>
+                  <c:v>4.6723711904761913</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.9846725714285718</c:v>
+                  <c:v>2.9198205714285717</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.3154152380952382</c:v>
+                  <c:v>1.3182723809523809</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.1081906857142858</c:v>
+                  <c:v>4.1224764</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.6045581714285708</c:v>
+                  <c:v>3.7617804523809517</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.5289088571428571</c:v>
+                  <c:v>2.5431945714285713</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8416,22 +8416,22 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="6"/>
                       <c:pt idx="0">
-                        <c:v>0.38538629193454693</c:v>
+                        <c:v>0.40545908592659802</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>1.9690767410814602</c:v>
+                        <c:v>1.92629195924809</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.70343060860707929</c:v>
+                        <c:v>0.70495849248790421</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.96500494617582055</c:v>
+                        <c:v>0.9683606290055653</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.34592688785302977</c:v>
+                        <c:v>0.36101539850105097</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0.25674201595358959</c:v>
+                        <c:v>0.25819234227701232</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -16324,13 +16324,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>226863</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>44824</xdr:rowOff>
+      <xdr:rowOff>122579</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>136919</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>175916</xdr:rowOff>
+      <xdr:rowOff>253671</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -16348,8 +16348,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9361338" y="644899"/>
-          <a:ext cx="6968081" cy="5407942"/>
+          <a:off x="6711639" y="729069"/>
+          <a:ext cx="7079076" cy="5853867"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17430,13 +17430,13 @@
         </row>
         <row r="7">
           <cell r="B7">
-            <v>189</v>
+            <v>190</v>
           </cell>
           <cell r="D7">
             <v>0</v>
           </cell>
           <cell r="E7">
-            <v>1.0896982</v>
+            <v>0.98969819999999997</v>
           </cell>
           <cell r="F7">
             <v>1</v>
@@ -17471,7 +17471,7 @@
             <v>1.51</v>
           </cell>
           <cell r="J11">
-            <v>0.57719810000000005</v>
+            <v>0.47719810000000001</v>
           </cell>
           <cell r="L11">
             <v>1.51</v>
@@ -17490,7 +17490,7 @@
             <v>2.9201769</v>
           </cell>
           <cell r="J13">
-            <v>1.0896982</v>
+            <v>0.98969820000000008</v>
           </cell>
           <cell r="L13">
             <v>1.72</v>
@@ -17501,10 +17501,10 @@
             <v>209.6436889</v>
           </cell>
           <cell r="D14">
-            <v>209.5071714</v>
+            <v>209.40717140000001</v>
           </cell>
           <cell r="E14">
-            <v>0.91047889999999998</v>
+            <v>1.0104789000000001</v>
           </cell>
         </row>
         <row r="18">
@@ -17547,7 +17547,7 @@
             <v>1.2422732000000001</v>
           </cell>
           <cell r="L22">
-            <v>1.28019E-2</v>
+            <v>0.1128019</v>
           </cell>
         </row>
         <row r="23">
@@ -17764,19 +17764,19 @@
             <v>87</v>
           </cell>
           <cell r="D7">
-            <v>0</v>
+            <v>4.09524E-2</v>
           </cell>
           <cell r="E7">
-            <v>2.8276393047619064</v>
+            <v>3.0213570380952395</v>
           </cell>
           <cell r="F7">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="I7">
             <v>0.86600469999999996</v>
           </cell>
           <cell r="J7">
-            <v>5.2380866666666671E-2</v>
+            <v>9.3333266666666678E-2</v>
           </cell>
         </row>
         <row r="8">
@@ -17784,7 +17784,7 @@
             <v>3.5868700000000003E-2</v>
           </cell>
           <cell r="J8">
-            <v>0.12380952380952381</v>
+            <v>0.17142857142857143</v>
           </cell>
         </row>
         <row r="9">
@@ -17792,7 +17792,7 @@
             <v>0.7</v>
           </cell>
           <cell r="J9">
-            <v>0.87009533333333344</v>
+            <v>0.87295247619047611</v>
           </cell>
           <cell r="L9">
             <v>0.7</v>
@@ -17814,7 +17814,7 @@
             <v>2.77</v>
           </cell>
           <cell r="J11">
-            <v>0.20457828571428571</v>
+            <v>0.30686742857142857</v>
           </cell>
           <cell r="L11">
             <v>2.77</v>
@@ -17836,16 +17836,16 @@
             <v>53.942062300000003</v>
           </cell>
           <cell r="D13">
-            <v>54.324063104761898</v>
+            <v>54.517780838095234</v>
           </cell>
           <cell r="E13">
-            <v>0.9739284476190474</v>
+            <v>0.87163930476190465</v>
           </cell>
           <cell r="I13">
             <v>5.3121441000000003</v>
           </cell>
           <cell r="J13">
-            <v>1.9575439714285716</v>
+            <v>2.148404561904762</v>
           </cell>
           <cell r="L13">
             <v>4.4102706999999999</v>
@@ -17863,10 +17863,10 @@
         </row>
         <row r="20">
           <cell r="D20">
-            <v>24</v>
+            <v>23</v>
           </cell>
           <cell r="F20">
-            <v>12</v>
+            <v>11</v>
           </cell>
           <cell r="M20">
             <v>0</v>
@@ -17879,7 +17879,7 @@
         </row>
         <row r="22">
           <cell r="M22">
-            <v>0.11251811428571427</v>
+            <v>1.0228971428571456E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -17938,10 +17938,10 @@
             <v>59</v>
           </cell>
           <cell r="D7">
-            <v>0.10770914285714286</v>
+            <v>0.20576959523809524</v>
           </cell>
           <cell r="E7">
-            <v>2.900483433333334</v>
+            <v>3.1062530285714289</v>
           </cell>
           <cell r="F7">
             <v>3</v>
@@ -17950,7 +17950,7 @@
             <v>1.0174715000000001</v>
           </cell>
           <cell r="J7">
-            <v>0.56955540952380956</v>
+            <v>0.63694146666666662</v>
           </cell>
           <cell r="L7">
             <v>0.46</v>
@@ -17961,7 +17961,7 @@
             <v>0.25114839999999999</v>
           </cell>
           <cell r="J8">
-            <v>0.36874257142857148</v>
+            <v>0.25150961904761909</v>
           </cell>
           <cell r="L8">
             <v>0.25</v>
@@ -17994,7 +17994,7 @@
             <v>0.69</v>
           </cell>
           <cell r="J11">
-            <v>1.0301343095238096</v>
+            <v>1.1685178476190476</v>
           </cell>
           <cell r="L11">
             <v>0.69</v>
@@ -18016,16 +18016,16 @@
             <v>40.943432700000002</v>
           </cell>
           <cell r="D13">
-            <v>41.883763633333324</v>
+            <v>42.089533228571419</v>
           </cell>
           <cell r="E13">
-            <v>0.71522916190476193</v>
+            <v>0.60518557142857143</v>
           </cell>
           <cell r="I13">
             <v>8.2986198999999985</v>
           </cell>
           <cell r="J13">
-            <v>2.6680721952380955</v>
+            <v>2.756608838095238</v>
           </cell>
           <cell r="L13">
             <v>6.9099999999999993</v>
@@ -18033,7 +18033,7 @@
         </row>
         <row r="18">
           <cell r="L18">
-            <v>0.57053149047619045</v>
+            <v>0.56077619999999995</v>
           </cell>
         </row>
         <row r="19">
@@ -18059,7 +18059,7 @@
         </row>
         <row r="22">
           <cell r="L22">
-            <v>0.12945950000000001</v>
+            <v>2.9171200000000001E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -18118,10 +18118,10 @@
             <v>57</v>
           </cell>
           <cell r="D7">
-            <v>0</v>
+            <v>9.5238095238095247E-6</v>
           </cell>
           <cell r="E7">
-            <v>5.2190673904761926</v>
+            <v>5.2190769142857167</v>
           </cell>
           <cell r="F7">
             <v>5</v>
@@ -18141,7 +18141,7 @@
             <v>0.40113710000000002</v>
           </cell>
           <cell r="J8">
-            <v>0.99661000000000022</v>
+            <v>1.001371904761905</v>
           </cell>
         </row>
         <row r="9">
@@ -18190,16 +18190,16 @@
             <v>36.256671900000001</v>
           </cell>
           <cell r="D13">
-            <v>37.05116699047619</v>
+            <v>37.055928895238097</v>
           </cell>
           <cell r="E13">
-            <v>1.8145476285714284</v>
+            <v>1.8097857238095234</v>
           </cell>
           <cell r="I13">
             <v>6.4215473000000003</v>
           </cell>
           <cell r="J13">
-            <v>5.1329154857142862</v>
+            <v>5.137677390476191</v>
           </cell>
           <cell r="L13">
             <v>5.2162243000000004</v>
@@ -18212,7 +18212,7 @@
         </row>
         <row r="19">
           <cell r="L19">
-            <v>0.17557714285714288</v>
+            <v>0.1708152380952381</v>
           </cell>
         </row>
         <row r="20">
@@ -18289,13 +18289,13 @@
         </row>
         <row r="7">
           <cell r="B7">
-            <v>17</v>
+            <v>18</v>
           </cell>
           <cell r="D7">
-            <v>0</v>
+            <v>1.6549600000000001E-2</v>
           </cell>
           <cell r="E7">
-            <v>0.86303660000000004</v>
+            <v>0.87958619999999998</v>
           </cell>
           <cell r="F7">
             <v>8</v>
@@ -18336,7 +18336,7 @@
             <v>0.95</v>
           </cell>
           <cell r="J11">
-            <v>0.31461840000000002</v>
+            <v>0.33116800000000002</v>
           </cell>
           <cell r="L11">
             <v>0.95</v>
@@ -18355,19 +18355,19 @@
         </row>
         <row r="13">
           <cell r="C13">
-            <v>3.8853399</v>
+            <v>4.1102949000000004</v>
           </cell>
           <cell r="D13">
-            <v>4.0258928999999997</v>
+            <v>4.0424424999999999</v>
           </cell>
           <cell r="E13">
-            <v>0.82184729999999995</v>
+            <v>1.0304297</v>
           </cell>
           <cell r="I13">
             <v>2.4858199999999995</v>
           </cell>
           <cell r="J13">
-            <v>0.86303660000000004</v>
+            <v>0.87958619999999998</v>
           </cell>
           <cell r="L13">
             <v>1.6199999999999999</v>
@@ -18386,15 +18386,15 @@
             <v>0</v>
           </cell>
           <cell r="L19">
-            <v>0.14353640000000001</v>
+            <v>0.36849140000000002</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="F20">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="I20">
             <v>0</v>
@@ -18416,7 +18416,7 @@
             <v>0</v>
           </cell>
           <cell r="L22">
-            <v>0.34916540000000001</v>
+            <v>0.3327928</v>
           </cell>
         </row>
         <row r="23">
@@ -18475,10 +18475,10 @@
             <v>26</v>
           </cell>
           <cell r="D7">
-            <v>0.1</v>
+            <v>7.3509714285714289E-2</v>
           </cell>
           <cell r="E7">
-            <v>5.6634805666666672</v>
+            <v>5.8150255190476194</v>
           </cell>
           <cell r="F7">
             <v>1</v>
@@ -18487,7 +18487,7 @@
             <v>1.9179082999999999</v>
           </cell>
           <cell r="J7">
-            <v>2.1237009571428573</v>
+            <v>2.2466744809523811</v>
           </cell>
           <cell r="L7">
             <v>1.36</v>
@@ -18514,7 +18514,7 @@
             <v>1.4506756000000001</v>
           </cell>
           <cell r="J10">
-            <v>1.4603469142857144</v>
+            <v>1.4746326285714286</v>
           </cell>
           <cell r="L10">
             <v>1.45</v>
@@ -18536,7 +18536,7 @@
             <v>2.61</v>
           </cell>
           <cell r="J12">
-            <v>1.5093696190476189</v>
+            <v>1.5236553333333331</v>
           </cell>
           <cell r="L12">
             <v>2.14</v>
@@ -18544,22 +18544,22 @@
         </row>
         <row r="13">
           <cell r="C13">
-            <v>30.033064599999999</v>
+            <v>30.226488</v>
           </cell>
           <cell r="D13">
-            <v>28.111590066666661</v>
+            <v>28.263135019047613</v>
           </cell>
           <cell r="E13">
-            <v>2.6420232619047619</v>
+            <v>2.6745860238095234</v>
           </cell>
           <cell r="I13">
             <v>8.9900771000000006</v>
           </cell>
           <cell r="J13">
-            <v>5.6634805666666672</v>
+            <v>5.8150255190476194</v>
           </cell>
           <cell r="K13">
-            <v>0.6299701886501804</v>
+            <v>0.64682710218888106</v>
           </cell>
           <cell r="L13">
             <v>7.7800000000000011</v>
@@ -18567,7 +18567,7 @@
         </row>
         <row r="18">
           <cell r="L18">
-            <v>0.96932516190476192</v>
+            <v>0.83242155238095239</v>
           </cell>
         </row>
         <row r="19">
@@ -18588,7 +18588,7 @@
         </row>
         <row r="21">
           <cell r="L21">
-            <v>0</v>
+            <v>0.16946637142857127</v>
           </cell>
         </row>
         <row r="22">
@@ -18974,7 +18974,7 @@
       <c r="H1" s="97"/>
       <c r="I1" s="98">
         <f ca="1">TODAY()</f>
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="L1" s="110"/>
       <c r="M1" s="110" t="s">
@@ -19003,16 +19003,16 @@
     <row r="3" spans="2:32" ht="134.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="100" t="str">
         <f>CONCATENATE("₹ ",ROUND($N$27,2)," / ",ROUND($M$27,2)," (",ROUND($O$27,3)*100,"%)")</f>
-        <v>₹ 16.8 / 35.31 (47.6%)</v>
+        <v>₹ 17.14 / 35.31 (48.5%)</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="85" t="str">
         <f ca="1">CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
-        <v>₹ 0.21  |  ₹ 17.99</v>
+        <v>₹ 0.32  |  ₹ 18.44</v>
       </c>
       <c r="G3" s="244" t="str">
         <f ca="1">CONCATENATE($U$11, "    |    ", $T$11)</f>
-        <v>25    |    43</v>
+        <v>24    |    42</v>
       </c>
       <c r="H3" s="245"/>
       <c r="I3" s="246"/>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="M4" s="80">
         <f>'[1]Project Summary'!$B$7</f>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N4" s="101">
         <f ca="1">'[1]Project Summary'!$D$7</f>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="O4" s="101">
         <f>'[1]Project Summary'!$E$7</f>
-        <v>1.0896982</v>
+        <v>0.98969819999999997</v>
       </c>
       <c r="P4" s="104">
         <f>'[1]Project Summary'!$F$7</f>
@@ -19096,11 +19096,11 @@
       </c>
       <c r="R4" s="79">
         <f>'[1]Project Summary'!$D$14</f>
-        <v>209.5071714</v>
+        <v>209.40717140000001</v>
       </c>
       <c r="S4" s="79">
         <f>'[1]Project Summary'!$E$14</f>
-        <v>0.91047889999999998</v>
+        <v>1.0104789000000001</v>
       </c>
       <c r="T4" s="69">
         <f>'[1]Project Summary'!$D$21</f>
@@ -19185,7 +19185,7 @@
     <row r="6" spans="2:32" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="84">
         <f>$S$11</f>
-        <v>10.136111652380951</v>
+        <v>10.051579776190476</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="9"/>
@@ -19195,7 +19195,7 @@
       </c>
       <c r="G6" s="250" t="str">
         <f>CONCATENATE($P$11," / ",V11)</f>
-        <v>11 / 18</v>
+        <v>12 / 18</v>
       </c>
       <c r="H6" s="251"/>
       <c r="I6" s="252"/>
@@ -19208,15 +19208,15 @@
       </c>
       <c r="N6" s="102">
         <f ca="1">'[3]Project Summary'!$D$7</f>
-        <v>0</v>
+        <v>4.09524E-2</v>
       </c>
       <c r="O6" s="102">
         <f>'[3]Project Summary'!$E$7</f>
-        <v>2.8276393047619064</v>
+        <v>3.0213570380952395</v>
       </c>
       <c r="P6" s="105">
         <f>'[3]Project Summary'!$F$7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="82">
         <f>'[3]Project Summary'!$C$13</f>
@@ -19224,19 +19224,19 @@
       </c>
       <c r="R6" s="82">
         <f>'[3]Project Summary'!$D$13</f>
-        <v>54.324063104761898</v>
+        <v>54.517780838095234</v>
       </c>
       <c r="S6" s="82">
         <f>'[3]Project Summary'!$E$13</f>
-        <v>0.9739284476190474</v>
+        <v>0.87163930476190465</v>
       </c>
       <c r="T6" s="69">
         <f>'[3]Project Summary'!$D$20</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U6" s="69">
         <f ca="1">'[3]Project Summary'!$F$20</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V6" s="69">
         <f>'[3]Project Summary'!$Q$3</f>
@@ -19275,11 +19275,11 @@
       </c>
       <c r="N7" s="102">
         <f ca="1">'[4]Project Summary'!$D$7</f>
-        <v>0.10770914285714286</v>
+        <v>0.20576959523809524</v>
       </c>
       <c r="O7" s="102">
         <f>'[4]Project Summary'!$E$7</f>
-        <v>2.900483433333334</v>
+        <v>3.1062530285714289</v>
       </c>
       <c r="P7" s="105">
         <f>'[4]Project Summary'!$F$7</f>
@@ -19291,11 +19291,11 @@
       </c>
       <c r="R7" s="82">
         <f>'[4]Project Summary'!$D$13</f>
-        <v>41.883763633333324</v>
+        <v>42.089533228571419</v>
       </c>
       <c r="S7" s="82">
         <f>'[4]Project Summary'!$E$13</f>
-        <v>0.71522916190476193</v>
+        <v>0.60518557142857143</v>
       </c>
       <c r="T7" s="69">
         <f>'[4]Project Summary'!$D$20</f>
@@ -19330,11 +19330,11 @@
       </c>
       <c r="N8" s="102">
         <f ca="1">'[5]Project Summary'!$D$7</f>
-        <v>0</v>
+        <v>9.5238095238095247E-6</v>
       </c>
       <c r="O8" s="102">
         <f>'[5]Project Summary'!$E$7</f>
-        <v>5.2190673904761926</v>
+        <v>5.2190769142857167</v>
       </c>
       <c r="P8" s="105">
         <f>'[5]Project Summary'!$F$7</f>
@@ -19346,11 +19346,11 @@
       </c>
       <c r="R8" s="82">
         <f>'[5]Project Summary'!$D$13</f>
-        <v>37.05116699047619</v>
+        <v>37.055928895238097</v>
       </c>
       <c r="S8" s="82">
         <f>'[5]Project Summary'!$E$13</f>
-        <v>1.8145476285714284</v>
+        <v>1.8097857238095234</v>
       </c>
       <c r="T8" s="69">
         <f>'[5]Project Summary'!$D$20</f>
@@ -19426,11 +19426,11 @@
       </c>
       <c r="N10" s="102">
         <f ca="1">'[7]Project Summary'!$D$7</f>
-        <v>0.1</v>
+        <v>7.3509714285714289E-2</v>
       </c>
       <c r="O10" s="103">
         <f>'[7]Project Summary'!$E$7</f>
-        <v>5.6634805666666672</v>
+        <v>5.8150255190476194</v>
       </c>
       <c r="P10" s="106">
         <f>'[7]Project Summary'!$F$7</f>
@@ -19438,15 +19438,15 @@
       </c>
       <c r="Q10" s="82">
         <f>'[7]Project Summary'!$C$13</f>
-        <v>30.033064599999999</v>
+        <v>30.226488</v>
       </c>
       <c r="R10" s="82">
         <f>'[7]Project Summary'!$D$13</f>
-        <v>28.111590066666661</v>
+        <v>28.263135019047613</v>
       </c>
       <c r="S10" s="82">
         <f>'[7]Project Summary'!$E$13</f>
-        <v>2.6420232619047619</v>
+        <v>2.6745860238095234</v>
       </c>
       <c r="T10" s="69">
         <f>'[7]Project Summary'!$D$20</f>
@@ -19476,39 +19476,39 @@
       </c>
       <c r="M11" s="117">
         <f>SUM(M4:M10)</f>
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N11" s="118">
         <f t="shared" ref="N11:W11" ca="1" si="0">SUM(N4:N10)</f>
-        <v>0.20770914285714287</v>
+        <v>0.32024123333333332</v>
       </c>
       <c r="O11" s="118">
         <f>SUM(O4:O10)</f>
-        <v>17.993011371428576</v>
+        <v>18.444053176190479</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="120">
         <f t="shared" si="0"/>
-        <v>552.01393680000001</v>
+        <v>552.20736020000004</v>
       </c>
       <c r="R11" s="120">
         <f t="shared" si="0"/>
-        <v>549.2109988714285</v>
+        <v>549.66679305714274</v>
       </c>
       <c r="S11" s="120">
         <f t="shared" si="0"/>
-        <v>10.136111652380951</v>
+        <v>10.051579776190476</v>
       </c>
       <c r="T11" s="121">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U11" s="121">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V11" s="121">
         <f t="shared" si="0"/>
@@ -19613,11 +19613,11 @@
       </c>
       <c r="N20" s="18">
         <f>'[1]Project Summary'!$J$13</f>
-        <v>1.0896982</v>
+        <v>0.98969820000000008</v>
       </c>
       <c r="O20" s="19">
         <f t="shared" ref="O20:O25" si="1">N20/M20</f>
-        <v>0.37316170811432692</v>
+        <v>0.33891720737877218</v>
       </c>
       <c r="P20" s="18">
         <f>'[1]Project Summary'!$L$13</f>
@@ -19625,7 +19625,7 @@
       </c>
       <c r="Q20" s="153">
         <f>M20-N20</f>
-        <v>1.8304787</v>
+        <v>1.9304786999999999</v>
       </c>
       <c r="S20" s="65" t="s">
         <v>41</v>
@@ -19636,11 +19636,11 @@
       </c>
       <c r="U20" s="64">
         <f>N43</f>
-        <v>4.4377010095238099</v>
+        <v>4.6690129904761903</v>
       </c>
       <c r="V20" s="88">
         <f>O43</f>
-        <v>0.38303105484821071</v>
+        <v>0.40299627374715741</v>
       </c>
       <c r="W20" s="64">
         <f>P43</f>
@@ -19685,11 +19685,11 @@
       </c>
       <c r="U21" s="64">
         <f>R43</f>
-        <v>2.4396125714285715</v>
+        <v>2.3747605714285718</v>
       </c>
       <c r="V21" s="88">
         <f>S43</f>
-        <v>2.6872072821538473</v>
+        <v>2.6157734943863935</v>
       </c>
       <c r="W21" s="64">
         <f>T43</f>
@@ -19711,11 +19711,11 @@
       </c>
       <c r="N22" s="18">
         <f>'[3]Project Summary'!$J$13</f>
-        <v>1.9575439714285716</v>
+        <v>2.148404561904762</v>
       </c>
       <c r="O22" s="19">
         <f t="shared" si="1"/>
-        <v>0.36850355234688975</v>
+        <v>0.4044326587271535</v>
       </c>
       <c r="P22" s="18">
         <f>'[3]Project Summary'!$L$13</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="Q22" s="153">
         <f t="shared" si="2"/>
-        <v>3.3546001285714286</v>
+        <v>3.1637395380952382</v>
       </c>
       <c r="S22" s="65" t="s">
         <v>45</v>
@@ -19734,11 +19734,11 @@
       </c>
       <c r="U22" s="64">
         <f>V43</f>
-        <v>1.3154152380952382</v>
+        <v>1.3182723809523809</v>
       </c>
       <c r="V22" s="88">
         <f>W43</f>
-        <v>1.019701734957549</v>
+        <v>1.0219165743816905</v>
       </c>
       <c r="W22" s="64">
         <f>X43</f>
@@ -19760,11 +19760,11 @@
       </c>
       <c r="N23" s="18">
         <f>'[4]Project Summary'!$J$13</f>
-        <v>2.6680721952380955</v>
+        <v>2.756608838095238</v>
       </c>
       <c r="O23" s="19">
         <f>N23/M23</f>
-        <v>0.32150794076471628</v>
+        <v>0.33217678015295515</v>
       </c>
       <c r="P23" s="18">
         <f>'[4]Project Summary'!$L$13</f>
@@ -19772,7 +19772,7 @@
       </c>
       <c r="Q23" s="153">
         <f t="shared" si="2"/>
-        <v>5.630547704761903</v>
+        <v>5.5420110619047609</v>
       </c>
       <c r="S23" s="65" t="str">
         <f>CONCATENATE("Demand For Registrations 
@@ -19786,11 +19786,11 @@
       </c>
       <c r="U23" s="64">
         <f>Z43</f>
-        <v>4.1081906857142858</v>
+        <v>4.1224764</v>
       </c>
       <c r="V23" s="88">
         <f>AA43</f>
-        <v>0.96500494617582055</v>
+        <v>0.9683606290055653</v>
       </c>
       <c r="W23" s="64">
         <f>AB43</f>
@@ -19812,11 +19812,11 @@
       </c>
       <c r="N24" s="18">
         <f>'[5]Project Summary'!$J$13</f>
-        <v>5.1329154857142862</v>
+        <v>5.137677390476191</v>
       </c>
       <c r="O24" s="19">
         <f>N24/M24</f>
-        <v>0.79932689831846071</v>
+        <v>0.8000684493091238</v>
       </c>
       <c r="P24" s="18">
         <f>'[5]Project Summary'!$L$13</f>
@@ -19838,11 +19838,11 @@
       </c>
       <c r="U24" s="64">
         <f>AD43</f>
-        <v>3.2899397714285707</v>
+        <v>3.4306124523809518</v>
       </c>
       <c r="V24" s="88">
         <f>AE43</f>
-        <v>0.34740652285412571</v>
+        <v>0.36226108261678475</v>
       </c>
       <c r="W24" s="64">
         <f>AF43</f>
@@ -19884,11 +19884,11 @@
       </c>
       <c r="U25" s="64">
         <f>AH43</f>
-        <v>2.5289088571428571</v>
+        <v>2.5431945714285713</v>
       </c>
       <c r="V25" s="88">
         <f>AI43</f>
-        <v>0.27820779506522081</v>
+        <v>0.27977938079522235</v>
       </c>
       <c r="W25" s="64">
         <f>AJ43</f>
@@ -19910,11 +19910,11 @@
       </c>
       <c r="N26" s="18">
         <f>'[7]Project Summary'!$J$13</f>
-        <v>5.6634805666666672</v>
+        <v>5.8150255190476194</v>
       </c>
       <c r="O26" s="19">
         <f>'[7]Project Summary'!$K$13</f>
-        <v>0.6299701886501804</v>
+        <v>0.64682710218888106</v>
       </c>
       <c r="P26" s="18">
         <f>'[7]Project Summary'!$L$13</f>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="Q26" s="153">
         <f t="shared" si="2"/>
-        <v>3.3265965333333334</v>
+        <v>3.1750515809523812</v>
       </c>
       <c r="AF26" s="1"/>
     </row>
@@ -19936,11 +19936,11 @@
       </c>
       <c r="N27" s="18">
         <f>SUM(N20:N26)</f>
-        <v>16.804352895238097</v>
+        <v>17.140056985714288</v>
       </c>
       <c r="O27" s="19">
         <f>N27/M27</f>
-        <v>0.47589866566520367</v>
+        <v>0.48540579335479433</v>
       </c>
       <c r="P27" s="18">
         <f>SUM(P20:P26)</f>
@@ -19948,7 +19948,7 @@
       </c>
       <c r="Q27" s="153">
         <f t="shared" si="2"/>
-        <v>18.506426704761907</v>
+        <v>18.170722614285715</v>
       </c>
       <c r="AF27" s="1"/>
     </row>
@@ -20018,7 +20018,7 @@
       <c r="AB34" s="237"/>
       <c r="AC34" s="232" t="str">
         <f ca="1">CONCATENATE("Expected Registrations in August ",$D$3,"'",$E$3," ")</f>
-        <v xml:space="preserve">Expected Registrations in August '₹ 0.21  |  ₹ 17.99 </v>
+        <v xml:space="preserve">Expected Registrations in August '₹ 0.32  |  ₹ 18.44 </v>
       </c>
       <c r="AD34" s="233"/>
       <c r="AE34" s="233"/>
@@ -20185,11 +20185,11 @@
       </c>
       <c r="AD36" s="128">
         <f>'[1]Project Summary'!$J$11</f>
-        <v>0.57719810000000005</v>
+        <v>0.47719810000000001</v>
       </c>
       <c r="AE36" s="129">
         <f>AD36/AC36</f>
-        <v>0.38225039735099342</v>
+        <v>0.31602523178807945</v>
       </c>
       <c r="AF36" s="145">
         <f>'[1]Project Summary'!$L$11</f>
@@ -20333,11 +20333,11 @@
       </c>
       <c r="N38" s="63">
         <f>'[3]Project Summary'!$J$7</f>
-        <v>5.2380866666666671E-2</v>
+        <v>9.3333266666666678E-2</v>
       </c>
       <c r="O38" s="88">
         <f t="shared" si="4"/>
-        <v>6.0485660951570673E-2</v>
+        <v>0.10777454979940257</v>
       </c>
       <c r="P38" s="146">
         <f>'[3]Project Summary'!$L$7</f>
@@ -20349,11 +20349,11 @@
       </c>
       <c r="R38" s="63">
         <f>'[3]Project Summary'!$J$8</f>
-        <v>0.12380952380952381</v>
+        <v>0.17142857142857143</v>
       </c>
       <c r="S38" s="88">
         <f t="shared" si="5"/>
-        <v>3.4517427118775923</v>
+        <v>4.779336062599743</v>
       </c>
       <c r="T38" s="124">
         <f>'[3]Project Summary'!$L$8</f>
@@ -20365,11 +20365,11 @@
       </c>
       <c r="V38" s="63">
         <f>'[3]Project Summary'!$J$9</f>
-        <v>0.87009533333333344</v>
+        <v>0.87295247619047611</v>
       </c>
       <c r="W38" s="88">
         <f t="shared" si="6"/>
-        <v>1.2429933333333336</v>
+        <v>1.2470749659863944</v>
       </c>
       <c r="X38" s="146">
         <f>'[3]Project Summary'!$L$9</f>
@@ -20397,11 +20397,11 @@
       </c>
       <c r="AD38" s="63">
         <f>'[3]Project Summary'!$J$11</f>
-        <v>0.20457828571428571</v>
+        <v>0.30686742857142857</v>
       </c>
       <c r="AE38" s="88">
         <f t="shared" si="9"/>
-        <v>7.3854976792160909E-2</v>
+        <v>0.11078246518824136</v>
       </c>
       <c r="AF38" s="146">
         <f>'[3]Project Summary'!$L$11</f>
@@ -20437,11 +20437,11 @@
       </c>
       <c r="N39" s="63">
         <f>'[4]Project Summary'!$J$7</f>
-        <v>0.56955540952380956</v>
+        <v>0.63694146666666662</v>
       </c>
       <c r="O39" s="88">
         <f t="shared" si="4"/>
-        <v>0.55977529544936588</v>
+        <v>0.6260042336976186</v>
       </c>
       <c r="P39" s="146">
         <f>'[4]Project Summary'!$L$7</f>
@@ -20453,11 +20453,11 @@
       </c>
       <c r="R39" s="63">
         <f>'[4]Project Summary'!$J$8</f>
-        <v>0.36874257142857148</v>
+        <v>0.25150961904761909</v>
       </c>
       <c r="S39" s="88">
         <f t="shared" si="5"/>
-        <v>1.4682258434796778</v>
+        <v>1.001438269356361</v>
       </c>
       <c r="T39" s="124">
         <f>'[4]Project Summary'!$L$8</f>
@@ -20501,11 +20501,11 @@
       </c>
       <c r="AD39" s="63">
         <f>'[4]Project Summary'!$J$11</f>
-        <v>1.0301343095238096</v>
+        <v>1.1685178476190476</v>
       </c>
       <c r="AE39" s="88">
         <f t="shared" si="9"/>
-        <v>1.4929482746721878</v>
+        <v>1.6935041269841271</v>
       </c>
       <c r="AF39" s="146">
         <f>'[4]Project Summary'!$L$11</f>
@@ -20557,11 +20557,11 @@
       </c>
       <c r="R40" s="63">
         <f>'[5]Project Summary'!$J$8</f>
-        <v>0.99661000000000022</v>
+        <v>1.001371904761905</v>
       </c>
       <c r="S40" s="88">
         <f t="shared" si="5"/>
-        <v>2.4844622948114252</v>
+        <v>2.4963333103866607</v>
       </c>
       <c r="T40" s="124">
         <f>'[5]Project Summary'!$L$8</f>
@@ -20731,11 +20731,11 @@
       </c>
       <c r="N42" s="63">
         <f>'[7]Project Summary'!$J$7</f>
-        <v>2.1237009571428573</v>
+        <v>2.2466744809523811</v>
       </c>
       <c r="O42" s="88">
         <f t="shared" si="4"/>
-        <v>1.1073005717441535</v>
+        <v>1.1714191345604903</v>
       </c>
       <c r="P42" s="146">
         <f>'[7]Project Summary'!$L$7</f>
@@ -20779,11 +20779,11 @@
       </c>
       <c r="Z42" s="63">
         <f>'[7]Project Summary'!$J$10</f>
-        <v>1.4603469142857144</v>
+        <v>1.4746326285714286</v>
       </c>
       <c r="AA42" s="88">
         <f t="shared" si="8"/>
-        <v>1.0066667656681578</v>
+        <v>1.0165143941012234</v>
       </c>
       <c r="AB42" s="146">
         <f>'[7]Project Summary'!$L$10</f>
@@ -20811,11 +20811,11 @@
       </c>
       <c r="AH42" s="63">
         <f>'[7]Project Summary'!$J$12</f>
-        <v>1.5093696190476189</v>
+        <v>1.5236553333333331</v>
       </c>
       <c r="AI42" s="88">
         <f t="shared" si="7"/>
-        <v>0.57830253603357051</v>
+        <v>0.58377598978288625</v>
       </c>
       <c r="AJ42" s="124">
         <f>'[7]Project Summary'!$L$12</f>
@@ -20835,11 +20835,11 @@
       </c>
       <c r="N43" s="125">
         <f>SUM(N36:N42)</f>
-        <v>4.4377010095238099</v>
+        <v>4.6690129904761903</v>
       </c>
       <c r="O43" s="126">
         <f>N43/M43</f>
-        <v>0.38303105484821071</v>
+        <v>0.40299627374715741</v>
       </c>
       <c r="P43" s="147">
         <f>SUM(P36:P42)</f>
@@ -20851,11 +20851,11 @@
       </c>
       <c r="R43" s="125">
         <f>SUM(R36:R42)</f>
-        <v>2.4396125714285715</v>
+        <v>2.3747605714285718</v>
       </c>
       <c r="S43" s="126">
         <f>R43/Q43</f>
-        <v>2.6872072821538473</v>
+        <v>2.6157734943863935</v>
       </c>
       <c r="T43" s="127">
         <f>SUM(T36:T42)</f>
@@ -20867,11 +20867,11 @@
       </c>
       <c r="V43" s="125">
         <f>SUM(V36:V42)</f>
-        <v>1.3154152380952382</v>
+        <v>1.3182723809523809</v>
       </c>
       <c r="W43" s="126">
         <f>V43/U43</f>
-        <v>1.019701734957549</v>
+        <v>1.0219165743816905</v>
       </c>
       <c r="X43" s="147">
         <f>SUM(X36:X42)</f>
@@ -20883,11 +20883,11 @@
       </c>
       <c r="Z43" s="125">
         <f>SUM(Z36:Z42)</f>
-        <v>4.1081906857142858</v>
+        <v>4.1224764</v>
       </c>
       <c r="AA43" s="126">
         <f>Z43/Y43</f>
-        <v>0.96500494617582055</v>
+        <v>0.9683606290055653</v>
       </c>
       <c r="AB43" s="147">
         <f>SUM(AB36:AB42)</f>
@@ -20899,11 +20899,11 @@
       </c>
       <c r="AD43" s="125">
         <f>SUM(AD36:AD42)</f>
-        <v>3.2899397714285707</v>
+        <v>3.4306124523809518</v>
       </c>
       <c r="AE43" s="126">
         <f>AD43/AC43</f>
-        <v>0.34740652285412571</v>
+        <v>0.36226108261678475</v>
       </c>
       <c r="AF43" s="147">
         <f>SUM(AF36:AF42)</f>
@@ -20915,11 +20915,11 @@
       </c>
       <c r="AH43" s="125">
         <f>SUM(AH36:AH42)</f>
-        <v>2.5289088571428571</v>
+        <v>2.5431945714285713</v>
       </c>
       <c r="AI43" s="126">
         <f>AH43/AG43</f>
-        <v>0.27820779506522081</v>
+        <v>0.27977938079522235</v>
       </c>
       <c r="AJ43" s="127">
         <f>SUM(AJ36:AJ42)</f>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="R45" s="112">
         <f>N27-R43</f>
-        <v>14.364740323809524</v>
+        <v>14.765296414285716</v>
       </c>
       <c r="S45" s="113"/>
       <c r="T45" s="112"/>
@@ -21122,7 +21122,7 @@
       </c>
       <c r="Z53" s="169">
         <f>'[4]Project Summary'!$L$18</f>
-        <v>0.57053149047619045</v>
+        <v>0.56077619999999995</v>
       </c>
       <c r="AA53" s="169">
         <f>'[5]Project Summary'!$L$18</f>
@@ -21133,11 +21133,11 @@
       </c>
       <c r="AC53" s="169">
         <f>'[7]Project Summary'!$L$18</f>
-        <v>0.96932516190476192</v>
+        <v>0.83242155238095239</v>
       </c>
       <c r="AD53" s="169">
         <f>SUM(W53:AC53)</f>
-        <v>7.2058061523809531</v>
+        <v>7.0591472523809538</v>
       </c>
     </row>
     <row r="54" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -21178,7 +21178,7 @@
       </c>
       <c r="AA54" s="169">
         <f>'[5]Project Summary'!$L$19</f>
-        <v>0.17557714285714288</v>
+        <v>0.1708152380952381</v>
       </c>
       <c r="AB54" s="169"/>
       <c r="AC54" s="169">
@@ -21187,7 +21187,7 @@
       </c>
       <c r="AD54" s="169">
         <f>SUM(W54:AC54)</f>
-        <v>0.78774791428571422</v>
+        <v>0.78298600952380948</v>
       </c>
     </row>
     <row r="55" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -21286,11 +21286,11 @@
       <c r="AB56" s="169"/>
       <c r="AC56" s="169">
         <f>'[7]Project Summary'!$L$21</f>
-        <v>0</v>
+        <v>0.16946637142857127</v>
       </c>
       <c r="AD56" s="169">
         <f>SUM(W56:AC56)</f>
-        <v>0.24146239523809523</v>
+        <v>0.4109287666666665</v>
       </c>
     </row>
     <row r="57" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -21318,7 +21318,7 @@
       </c>
       <c r="W57" s="168">
         <f>'[1]Project Summary'!$L$22</f>
-        <v>1.28019E-2</v>
+        <v>0.1128019</v>
       </c>
       <c r="X57" s="169">
         <f>'[2]Project Summary'!$L$22</f>
@@ -21326,11 +21326,11 @@
       </c>
       <c r="Y57" s="169">
         <f>'[3]Project Summary'!$M$22</f>
-        <v>0.11251811428571427</v>
+        <v>1.0228971428571456E-2</v>
       </c>
       <c r="Z57" s="169">
         <f>'[4]Project Summary'!$L$22</f>
-        <v>0.12945950000000001</v>
+        <v>2.9171200000000001E-2</v>
       </c>
       <c r="AA57" s="169">
         <f>'[5]Project Summary'!$L$22</f>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="AD57" s="169">
         <f>SUM(W57:AC57)</f>
-        <v>1.9022396904761905</v>
+        <v>1.7996622476190476</v>
       </c>
     </row>
     <row r="58" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -21368,7 +21368,7 @@
       </c>
       <c r="W58" s="167">
         <f t="shared" ref="W58:AD58" si="11">SUM(W53:W57)</f>
-        <v>0.91047889999999998</v>
+        <v>1.0104788999999998</v>
       </c>
       <c r="X58" s="167">
         <f t="shared" si="11"/>
@@ -21376,15 +21376,15 @@
       </c>
       <c r="Y58" s="167">
         <f t="shared" si="11"/>
-        <v>0.9739284476190474</v>
+        <v>0.87163930476190465</v>
       </c>
       <c r="Z58" s="167">
         <f t="shared" si="11"/>
-        <v>0.71522916190476193</v>
+        <v>0.60518557142857132</v>
       </c>
       <c r="AA58" s="167">
         <f t="shared" si="11"/>
-        <v>1.8145476285714284</v>
+        <v>1.8097857238095236</v>
       </c>
       <c r="AB58" s="167">
         <f t="shared" si="11"/>
@@ -21392,11 +21392,11 @@
       </c>
       <c r="AC58" s="167">
         <f t="shared" si="11"/>
-        <v>2.6420232619047619</v>
+        <v>2.6745860238095238</v>
       </c>
       <c r="AD58" s="167">
         <f t="shared" si="11"/>
-        <v>10.137256152380953</v>
+        <v>10.052724276190478</v>
       </c>
     </row>
     <row r="59" spans="12:30" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -21453,6 +21453,13 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="16">
+    <mergeCell ref="S18:V18"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="AG34:AJ34"/>
+    <mergeCell ref="AC34:AF34"/>
+    <mergeCell ref="Y34:AB34"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="Q34:T34"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="L52:Q52"/>
@@ -21462,13 +21469,6 @@
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="S18:V18"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="AG34:AJ34"/>
-    <mergeCell ref="AC34:AF34"/>
-    <mergeCell ref="Y34:AB34"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="Q34:T34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -21521,20 +21521,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:36" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="257" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="257"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
-      <c r="F1" s="257"/>
+      <c r="B1" s="254" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="254"/>
       <c r="H1" s="37" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="35"/>
       <c r="J1" s="36">
         <f ca="1">TODAY()</f>
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="Q1" s="235" t="s">
         <v>77</v>
@@ -21544,19 +21544,19 @@
       <c r="T1" s="235"/>
     </row>
     <row r="2" spans="2:36" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="258" t="s">
+      <c r="B2" s="255" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="258"/>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="C2" s="255"/>
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="258" t="s">
+      <c r="H2" s="255" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
@@ -21576,12 +21576,12 @@
         <f>$S$9</f>
         <v>0</v>
       </c>
-      <c r="H3" s="259" t="str">
+      <c r="H3" s="256" t="str">
         <f>CONCATENATE($Z$9, " / ", $Y$9)</f>
         <v>9 / 17</v>
       </c>
-      <c r="I3" s="260"/>
-      <c r="J3" s="261"/>
+      <c r="I3" s="257"/>
+      <c r="J3" s="258"/>
       <c r="L3" s="5">
         <v>8</v>
       </c>
@@ -21722,12 +21722,12 @@
         <f>$W$19</f>
         <v>6.6640613999999996</v>
       </c>
-      <c r="H6" s="254" t="str">
+      <c r="H6" s="259" t="str">
         <f>CONCATENATE($U$9," / ",AA9)</f>
         <v>17 / 20</v>
       </c>
-      <c r="I6" s="255"/>
-      <c r="J6" s="256"/>
+      <c r="I6" s="260"/>
+      <c r="J6" s="261"/>
       <c r="L6" s="10"/>
       <c r="Q6" s="11" t="s">
         <v>86</v>
@@ -22496,17 +22496,17 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="11">
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="V12:AA12"/>
+    <mergeCell ref="Q23:T23"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="V12:AA12"/>
-    <mergeCell ref="Q23:T23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -22565,10 +22565,13 @@
       </c>
       <c r="I1" s="98">
         <f ca="1">TODAY()</f>
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="K1" s="170"/>
-      <c r="L1" s="97"/>
+      <c r="L1" s="97">
+        <f>14.76+2.92+1.32</f>
+        <v>19</v>
+      </c>
       <c r="M1" s="110"/>
       <c r="N1" s="110"/>
       <c r="O1" s="110"/>
@@ -22599,13 +22602,13 @@
     <row r="3" spans="2:32" ht="134.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="239" t="str">
         <f>CONCATENATE("₹ ",ROUND($N$27,2)," / ",ROUND($M$27,2)," (",ROUND($O$27,3)*100,"%)")</f>
-        <v>₹ 14.68 / 36.05 (40.7%)</v>
+        <v>₹ 15.1 / 36.05 (41.9%)</v>
       </c>
       <c r="C3" s="240"/>
       <c r="D3" s="241"/>
       <c r="F3" s="161" t="str">
         <f>CONCATENATE("₹ ", ROUND($U$21,2), "  /  ", "₹ ", ROUND($T$21,2))</f>
-        <v>₹ 2.98  /  ₹ 1.52</v>
+        <v>₹ 2.92  /  ₹ 1.52</v>
       </c>
       <c r="G3" s="160" t="str">
         <f>CONCATENATE("₹ ", ROUND($U$22,2), "  /  ", "₹ ", ROUND($T$22,2))</f>
@@ -22613,7 +22616,7 @@
       </c>
       <c r="I3" s="85" t="str">
         <f ca="1">CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
-        <v>₹ 0.21  |  ₹ 18.86</v>
+        <v>₹ 0.34  |  ₹ 19.32</v>
       </c>
       <c r="L3" s="114" t="s">
         <v>5</v>
@@ -22676,7 +22679,7 @@
       </c>
       <c r="M4" s="80">
         <f>'[1]Project Summary'!$B$7</f>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N4" s="101">
         <f ca="1">'[1]Project Summary'!$D$7</f>
@@ -22684,7 +22687,7 @@
       </c>
       <c r="O4" s="101">
         <f>'[1]Project Summary'!$E$7</f>
-        <v>1.0896982</v>
+        <v>0.98969819999999997</v>
       </c>
       <c r="P4" s="104">
         <f>'[1]Project Summary'!$F$7</f>
@@ -22696,11 +22699,11 @@
       </c>
       <c r="R4" s="79">
         <f>'[1]Project Summary'!$D$14</f>
-        <v>209.5071714</v>
+        <v>209.40717140000001</v>
       </c>
       <c r="S4" s="79">
         <f>'[1]Project Summary'!$E$14</f>
-        <v>0.91047889999999998</v>
+        <v>1.0104789000000001</v>
       </c>
       <c r="T4" s="69">
         <f>'[1]Project Summary'!$D$21</f>
@@ -22787,7 +22790,7 @@
       <c r="C6" s="8"/>
       <c r="D6" s="84">
         <f>$S$11-AC54-AC55</f>
-        <v>9.7978191380952371</v>
+        <v>9.7016765666666664</v>
       </c>
       <c r="F6" s="154" t="str">
         <f ca="1">CONCATENATE($U$11, "      |    ", $T$11)</f>
@@ -22795,11 +22798,11 @@
       </c>
       <c r="G6" s="156" t="str">
         <f>CONCATENATE($P$11," / ",V11)</f>
-        <v>19 / 26</v>
+        <v>20 / 26</v>
       </c>
       <c r="I6" s="84">
         <f>$S$11</f>
-        <v>10.729103452380951</v>
+        <v>10.853153976190475</v>
       </c>
       <c r="L6" s="109" t="s">
         <v>116</v>
@@ -22810,15 +22813,15 @@
       </c>
       <c r="N6" s="102">
         <f ca="1">'[3]Project Summary'!$D$7</f>
-        <v>0</v>
+        <v>4.09524E-2</v>
       </c>
       <c r="O6" s="102">
         <f>'[3]Project Summary'!$E$7</f>
-        <v>2.8276393047619064</v>
+        <v>3.0213570380952395</v>
       </c>
       <c r="P6" s="105">
         <f>'[3]Project Summary'!$F$7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="82">
         <f>'[3]Project Summary'!$C$13</f>
@@ -22826,19 +22829,19 @@
       </c>
       <c r="R6" s="82">
         <f>'[3]Project Summary'!$D$13</f>
-        <v>54.324063104761898</v>
+        <v>54.517780838095234</v>
       </c>
       <c r="S6" s="82">
         <f>'[3]Project Summary'!$E$13</f>
-        <v>0.9739284476190474</v>
+        <v>0.87163930476190465</v>
       </c>
       <c r="T6" s="69">
         <f>'[3]Project Summary'!$D$20</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U6" s="69">
         <f ca="1">'[3]Project Summary'!$F$20</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V6" s="69">
         <f>'[3]Project Summary'!$Q$3</f>
@@ -22879,11 +22882,11 @@
       </c>
       <c r="N7" s="102">
         <f ca="1">'[4]Project Summary'!$D$7</f>
-        <v>0.10770914285714286</v>
+        <v>0.20576959523809524</v>
       </c>
       <c r="O7" s="102">
         <f>'[4]Project Summary'!$E$7</f>
-        <v>2.900483433333334</v>
+        <v>3.1062530285714289</v>
       </c>
       <c r="P7" s="105">
         <f>'[4]Project Summary'!$F$7</f>
@@ -22895,11 +22898,11 @@
       </c>
       <c r="R7" s="82">
         <f>'[4]Project Summary'!$D$13</f>
-        <v>41.883763633333324</v>
+        <v>42.089533228571419</v>
       </c>
       <c r="S7" s="82">
         <f>'[4]Project Summary'!$E$13</f>
-        <v>0.71522916190476193</v>
+        <v>0.60518557142857143</v>
       </c>
       <c r="T7" s="69">
         <f>'[4]Project Summary'!$D$20</f>
@@ -22933,11 +22936,11 @@
       </c>
       <c r="N8" s="102">
         <f ca="1">'[5]Project Summary'!$D$7</f>
-        <v>0</v>
+        <v>9.5238095238095247E-6</v>
       </c>
       <c r="O8" s="102">
         <f>'[5]Project Summary'!$E$7</f>
-        <v>5.2190673904761926</v>
+        <v>5.2190769142857167</v>
       </c>
       <c r="P8" s="105">
         <f>'[5]Project Summary'!$F$7</f>
@@ -22949,11 +22952,11 @@
       </c>
       <c r="R8" s="82">
         <f>'[5]Project Summary'!$D$13</f>
-        <v>37.05116699047619</v>
+        <v>37.055928895238097</v>
       </c>
       <c r="S8" s="82">
         <f>'[5]Project Summary'!$E$13</f>
-        <v>1.8145476285714284</v>
+        <v>1.8097857238095234</v>
       </c>
       <c r="T8" s="69">
         <f>'[5]Project Summary'!$D$20</f>
@@ -22982,15 +22985,15 @@
       </c>
       <c r="M9" s="69">
         <f>'[6]Project Summary'!$B$7</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N9" s="102">
-        <f ca="1">'[6]Project Summary'!$D$7</f>
-        <v>0</v>
+        <f>'[6]Project Summary'!$D$7</f>
+        <v>1.6549600000000001E-2</v>
       </c>
       <c r="O9" s="103">
         <f>'[6]Project Summary'!$E$7</f>
-        <v>0.86303660000000004</v>
+        <v>0.87958619999999998</v>
       </c>
       <c r="P9" s="106">
         <f>'[6]Project Summary'!$F$7</f>
@@ -22998,23 +23001,23 @@
       </c>
       <c r="Q9" s="82">
         <f>'[6]Project Summary'!$C$13</f>
-        <v>3.8853399</v>
+        <v>4.1102949000000004</v>
       </c>
       <c r="R9" s="82">
         <f>'[6]Project Summary'!$D$13</f>
-        <v>4.0258928999999997</v>
+        <v>4.0424424999999999</v>
       </c>
       <c r="S9" s="82">
         <f>'[6]Project Summary'!$E$13</f>
-        <v>0.82184729999999995</v>
+        <v>1.0304297</v>
       </c>
       <c r="T9" s="69">
         <f>'[6]Project Summary'!$D$20</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9" s="69">
-        <f ca="1">'[6]Project Summary'!$F$20</f>
-        <v>6</v>
+        <f>'[6]Project Summary'!$F$20</f>
+        <v>7</v>
       </c>
       <c r="V9" s="69">
         <f>'[6]Project Summary'!$Q$3</f>
@@ -23038,11 +23041,11 @@
       </c>
       <c r="N10" s="102">
         <f ca="1">'[7]Project Summary'!$D$7</f>
-        <v>0.1</v>
+        <v>7.3509714285714289E-2</v>
       </c>
       <c r="O10" s="103">
         <f>'[7]Project Summary'!$E$7</f>
-        <v>5.6634805666666672</v>
+        <v>5.8150255190476194</v>
       </c>
       <c r="P10" s="106">
         <f>'[7]Project Summary'!$F$7</f>
@@ -23050,15 +23053,15 @@
       </c>
       <c r="Q10" s="82">
         <f>'[7]Project Summary'!$C$13</f>
-        <v>30.033064599999999</v>
+        <v>30.226488</v>
       </c>
       <c r="R10" s="82">
         <f>'[7]Project Summary'!$D$13</f>
-        <v>28.111590066666661</v>
+        <v>28.263135019047613</v>
       </c>
       <c r="S10" s="82">
         <f>'[7]Project Summary'!$E$13</f>
-        <v>2.6420232619047619</v>
+        <v>2.6745860238095234</v>
       </c>
       <c r="T10" s="69">
         <f>'[7]Project Summary'!$D$20</f>
@@ -23086,31 +23089,31 @@
       </c>
       <c r="M11" s="117">
         <f t="shared" ref="M11:W11" si="0">SUM(M4:M10)</f>
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N11" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>0.20770914285714287</v>
+        <v>0.33679083333333337</v>
       </c>
       <c r="O11" s="118">
         <f t="shared" si="0"/>
-        <v>18.856047971428577</v>
+        <v>19.323639376190481</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q11" s="120">
         <f t="shared" si="0"/>
-        <v>477.31268460000007</v>
+        <v>477.73106300000006</v>
       </c>
       <c r="R11" s="120">
         <f t="shared" si="0"/>
-        <v>474.87915517142852</v>
+        <v>475.35149895714284</v>
       </c>
       <c r="S11" s="120">
         <f t="shared" si="0"/>
-        <v>10.729103452380951</v>
+        <v>10.853153976190475</v>
       </c>
       <c r="T11" s="121">
         <f t="shared" si="0"/>
@@ -23224,11 +23227,11 @@
       </c>
       <c r="N20" s="18">
         <f>'[1]Project Summary'!$J$13-R36</f>
-        <v>0.68969819999999993</v>
+        <v>0.58969820000000006</v>
       </c>
       <c r="O20" s="19">
         <f t="shared" ref="O20:O25" si="1">N20/M20</f>
-        <v>0.23618370517210788</v>
+        <v>0.20193920443655317</v>
       </c>
       <c r="P20" s="18">
         <f>'[1]Project Summary'!$L$13-T36</f>
@@ -23236,7 +23239,7 @@
       </c>
       <c r="Q20" s="18">
         <f t="shared" ref="Q20:Q27" si="2">P20-N20</f>
-        <v>1.0303018000000002</v>
+        <v>1.1303017999999998</v>
       </c>
       <c r="R20" s="228">
         <f>M20-P20</f>
@@ -23251,11 +23254,11 @@
       </c>
       <c r="U20" s="64">
         <f>N43</f>
-        <v>4.4410592095238099</v>
+        <v>4.6723711904761913</v>
       </c>
       <c r="V20" s="88">
         <f>O43</f>
-        <v>0.38538629193454693</v>
+        <v>0.40545908592659802</v>
       </c>
       <c r="W20" s="64">
         <f>P43</f>
@@ -23304,11 +23307,11 @@
       </c>
       <c r="U21" s="64">
         <f>R43</f>
-        <v>2.9846725714285718</v>
+        <v>2.9198205714285717</v>
       </c>
       <c r="V21" s="88">
         <f>S43</f>
-        <v>1.9690767410814602</v>
+        <v>1.92629195924809</v>
       </c>
       <c r="W21" s="64">
         <f>T43</f>
@@ -23330,11 +23333,11 @@
       </c>
       <c r="N22" s="18">
         <f>'[3]Project Summary'!$J$13-R38</f>
-        <v>1.8337344476190478</v>
+        <v>1.9769759904761905</v>
       </c>
       <c r="O22" s="19">
         <f t="shared" si="1"/>
-        <v>0.34754335371103784</v>
+        <v>0.37469158461216606</v>
       </c>
       <c r="P22" s="18">
         <f>'[3]Project Summary'!$L$13-T38</f>
@@ -23342,7 +23345,7 @@
       </c>
       <c r="Q22" s="18">
         <f t="shared" si="2"/>
-        <v>2.5765362523809521</v>
+        <v>2.4332947095238096</v>
       </c>
       <c r="R22" s="228">
         <f t="shared" si="3"/>
@@ -23357,11 +23360,11 @@
       </c>
       <c r="U22" s="64">
         <f>V43</f>
-        <v>1.3154152380952382</v>
+        <v>1.3182723809523809</v>
       </c>
       <c r="V22" s="88">
         <f>W43</f>
-        <v>0.70343060860707929</v>
+        <v>0.70495849248790421</v>
       </c>
       <c r="W22" s="64">
         <f>X43</f>
@@ -23383,11 +23386,11 @@
       </c>
       <c r="N23" s="18">
         <f>'[4]Project Summary'!$J$13-R39</f>
-        <v>2.2993296238095242</v>
+        <v>2.5050992190476191</v>
       </c>
       <c r="O23" s="19">
         <f t="shared" si="1"/>
-        <v>0.28572075388021251</v>
+        <v>0.31129022563765768</v>
       </c>
       <c r="P23" s="18">
         <f>'[4]Project Summary'!$L$13-T39</f>
@@ -23395,7 +23398,7 @@
       </c>
       <c r="Q23" s="18">
         <f t="shared" si="2"/>
-        <v>4.360670376190475</v>
+        <v>4.1549007809523797</v>
       </c>
       <c r="R23" s="228">
         <f t="shared" si="3"/>
@@ -23413,11 +23416,11 @@
       </c>
       <c r="U23" s="64">
         <f>Z43</f>
-        <v>4.1081906857142858</v>
+        <v>4.1224764</v>
       </c>
       <c r="V23" s="88">
         <f>AA43</f>
-        <v>0.96500494617582055</v>
+        <v>0.9683606290055653</v>
       </c>
       <c r="W23" s="64">
         <f>AB43</f>
@@ -23469,11 +23472,11 @@
       </c>
       <c r="U24" s="64">
         <f>AD43</f>
-        <v>3.6045581714285708</v>
+        <v>3.7617804523809517</v>
       </c>
       <c r="V24" s="88">
         <f>AE43</f>
-        <v>0.34592688785302977</v>
+        <v>0.36101539850105097</v>
       </c>
       <c r="W24" s="64">
         <f>AF43</f>
@@ -23495,11 +23498,11 @@
       </c>
       <c r="N25" s="18">
         <f>'[6]Project Summary'!$J$13-R41</f>
-        <v>0.31797660000000005</v>
+        <v>0.3345262</v>
       </c>
       <c r="O25" s="19">
         <f t="shared" si="1"/>
-        <v>0.16932480917207343</v>
+        <v>0.17813758930078144</v>
       </c>
       <c r="P25" s="18">
         <f>'[6]Project Summary'!$L$13-T41</f>
@@ -23507,7 +23510,7 @@
       </c>
       <c r="Q25" s="18">
         <f t="shared" si="2"/>
-        <v>1.3020233999999999</v>
+        <v>1.2854737999999999</v>
       </c>
       <c r="R25" s="228">
         <f t="shared" si="3"/>
@@ -23522,11 +23525,11 @@
       </c>
       <c r="U25" s="64">
         <f>AH43</f>
-        <v>2.5289088571428571</v>
+        <v>2.5431945714285713</v>
       </c>
       <c r="V25" s="88">
         <f>AI43</f>
-        <v>0.25674201595358959</v>
+        <v>0.25819234227701232</v>
       </c>
       <c r="W25" s="64">
         <f>AJ43</f>
@@ -23548,11 +23551,11 @@
       </c>
       <c r="N26" s="18">
         <f>'[7]Project Summary'!$J$13-R42</f>
-        <v>5.1130300904761912</v>
+        <v>5.2645750428571434</v>
       </c>
       <c r="O26" s="19">
         <f>'[7]Project Summary'!$K$13</f>
-        <v>0.6299701886501804</v>
+        <v>0.64682710218888106</v>
       </c>
       <c r="P26" s="18">
         <f>'[7]Project Summary'!$L$13-T42</f>
@@ -23560,7 +23563,7 @@
       </c>
       <c r="Q26" s="18">
         <f t="shared" si="2"/>
-        <v>2.66696990952381</v>
+        <v>2.5154249571428577</v>
       </c>
       <c r="R26" s="228">
         <f t="shared" si="3"/>
@@ -23578,11 +23581,11 @@
       </c>
       <c r="N27" s="18">
         <f>SUM(N20:N26)</f>
-        <v>14.682716923809526</v>
+        <v>15.099822614285713</v>
       </c>
       <c r="O27" s="19">
         <f>N27/M27</f>
-        <v>0.40727822759265764</v>
+        <v>0.41884816163262256</v>
       </c>
       <c r="P27" s="18">
         <f>SUM(P20:P26)</f>
@@ -23590,7 +23593,7 @@
       </c>
       <c r="Q27" s="18">
         <f t="shared" si="2"/>
-        <v>13.223778076190477</v>
+        <v>12.80667238571429</v>
       </c>
       <c r="R27" s="228">
         <f>M27-P27</f>
@@ -23670,7 +23673,7 @@
       <c r="AB34" s="237"/>
       <c r="AC34" s="232" t="str">
         <f ca="1">CONCATENATE("Expected Registrations in August ",$D$3,"'",$I$3," ")</f>
-        <v xml:space="preserve">Expected Registrations in August '₹ 0.21  |  ₹ 18.86 </v>
+        <v xml:space="preserve">Expected Registrations in August '₹ 0.34  |  ₹ 19.32 </v>
       </c>
       <c r="AD34" s="233"/>
       <c r="AE34" s="233"/>
@@ -23851,11 +23854,11 @@
       </c>
       <c r="AD36" s="128">
         <f>'[1]Project Summary'!$J$11</f>
-        <v>0.57719810000000005</v>
+        <v>0.47719810000000001</v>
       </c>
       <c r="AE36" s="129">
         <f t="shared" ref="AE36:AE43" si="11">AD36/AC36</f>
-        <v>0.38225039735099342</v>
+        <v>0.31602523178807945</v>
       </c>
       <c r="AF36" s="145">
         <f>'[1]Project Summary'!$L$11</f>
@@ -24003,11 +24006,11 @@
       </c>
       <c r="N38" s="63">
         <f>'[3]Project Summary'!$J$7</f>
-        <v>5.2380866666666671E-2</v>
+        <v>9.3333266666666678E-2</v>
       </c>
       <c r="O38" s="88">
         <f t="shared" si="7"/>
-        <v>6.0485660951570673E-2</v>
+        <v>0.10777454979940257</v>
       </c>
       <c r="P38" s="146">
         <f>'[3]Project Summary'!$L$7</f>
@@ -24019,11 +24022,11 @@
       </c>
       <c r="R38" s="63">
         <f>'[3]Project Summary'!$J$8</f>
-        <v>0.12380952380952381</v>
+        <v>0.17142857142857143</v>
       </c>
       <c r="S38" s="88">
         <f t="shared" si="8"/>
-        <v>3.4517427118775923</v>
+        <v>4.779336062599743</v>
       </c>
       <c r="T38" s="124">
         <f>'[3]Project Summary'!$L$8</f>
@@ -24035,11 +24038,11 @@
       </c>
       <c r="V38" s="63">
         <f>'[3]Project Summary'!$J$9</f>
-        <v>0.87009533333333344</v>
+        <v>0.87295247619047611</v>
       </c>
       <c r="W38" s="88">
         <f t="shared" si="9"/>
-        <v>1.2429933333333336</v>
+        <v>1.2470749659863944</v>
       </c>
       <c r="X38" s="146">
         <f>'[3]Project Summary'!$L$9</f>
@@ -24067,11 +24070,11 @@
       </c>
       <c r="AD38" s="63">
         <f>'[3]Project Summary'!$J$11</f>
-        <v>0.20457828571428571</v>
+        <v>0.30686742857142857</v>
       </c>
       <c r="AE38" s="88">
         <f t="shared" si="11"/>
-        <v>7.3854976792160909E-2</v>
+        <v>0.11078246518824136</v>
       </c>
       <c r="AF38" s="146">
         <f>'[3]Project Summary'!$L$11</f>
@@ -24112,11 +24115,11 @@
       </c>
       <c r="N39" s="63">
         <f>'[4]Project Summary'!$J$7</f>
-        <v>0.56955540952380956</v>
+        <v>0.63694146666666662</v>
       </c>
       <c r="O39" s="88">
         <f t="shared" si="7"/>
-        <v>0.55977529544936588</v>
+        <v>0.6260042336976186</v>
       </c>
       <c r="P39" s="146">
         <f>'[4]Project Summary'!$L$7</f>
@@ -24128,11 +24131,11 @@
       </c>
       <c r="R39" s="63">
         <f>'[4]Project Summary'!$J$8</f>
-        <v>0.36874257142857148</v>
+        <v>0.25150961904761909</v>
       </c>
       <c r="S39" s="88">
         <f t="shared" si="8"/>
-        <v>1.4682258434796778</v>
+        <v>1.001438269356361</v>
       </c>
       <c r="T39" s="124">
         <f>'[4]Project Summary'!$L$8</f>
@@ -24176,11 +24179,11 @@
       </c>
       <c r="AD39" s="63">
         <f>'[4]Project Summary'!$J$11</f>
-        <v>1.0301343095238096</v>
+        <v>1.1685178476190476</v>
       </c>
       <c r="AE39" s="88">
         <f t="shared" si="11"/>
-        <v>1.4929482746721878</v>
+        <v>1.6935041269841271</v>
       </c>
       <c r="AF39" s="146">
         <f>'[4]Project Summary'!$L$11</f>
@@ -24237,11 +24240,11 @@
       </c>
       <c r="R40" s="63">
         <f>'[5]Project Summary'!$J$8</f>
-        <v>0.99661000000000022</v>
+        <v>1.001371904761905</v>
       </c>
       <c r="S40" s="88">
         <f t="shared" si="8"/>
-        <v>2.4844622948114252</v>
+        <v>2.4963333103866607</v>
       </c>
       <c r="T40" s="124">
         <f>'[5]Project Summary'!$L$8</f>
@@ -24394,11 +24397,11 @@
       </c>
       <c r="AD41" s="63">
         <f>'[6]Project Summary'!$J$11</f>
-        <v>0.31461840000000002</v>
+        <v>0.33116800000000002</v>
       </c>
       <c r="AE41" s="88">
         <f t="shared" si="11"/>
-        <v>0.33117726315789475</v>
+        <v>0.34859789473684216</v>
       </c>
       <c r="AF41" s="146">
         <f>'[6]Project Summary'!$L$11</f>
@@ -24441,11 +24444,11 @@
       </c>
       <c r="N42" s="63">
         <f>'[7]Project Summary'!$J$7</f>
-        <v>2.1237009571428573</v>
+        <v>2.2466744809523811</v>
       </c>
       <c r="O42" s="88">
         <f t="shared" si="7"/>
-        <v>1.1073005717441535</v>
+        <v>1.1714191345604903</v>
       </c>
       <c r="P42" s="146">
         <f>'[7]Project Summary'!$L$7</f>
@@ -24489,11 +24492,11 @@
       </c>
       <c r="Z42" s="63">
         <f>'[7]Project Summary'!$J$10</f>
-        <v>1.4603469142857144</v>
+        <v>1.4746326285714286</v>
       </c>
       <c r="AA42" s="88">
         <f t="shared" si="10"/>
-        <v>1.0066667656681578</v>
+        <v>1.0165143941012234</v>
       </c>
       <c r="AB42" s="146">
         <f>'[7]Project Summary'!$L$10</f>
@@ -24521,11 +24524,11 @@
       </c>
       <c r="AH42" s="63">
         <f>'[7]Project Summary'!$J$12</f>
-        <v>1.5093696190476189</v>
+        <v>1.5236553333333331</v>
       </c>
       <c r="AI42" s="88">
         <f t="shared" si="12"/>
-        <v>0.57830253603357051</v>
+        <v>0.58377598978288625</v>
       </c>
       <c r="AJ42" s="186">
         <f>'[7]Project Summary'!$L$12</f>
@@ -24550,11 +24553,11 @@
       </c>
       <c r="N43" s="192">
         <f>SUM(N36:N42)</f>
-        <v>4.4410592095238099</v>
+        <v>4.6723711904761913</v>
       </c>
       <c r="O43" s="193">
         <f t="shared" si="7"/>
-        <v>0.38538629193454693</v>
+        <v>0.40545908592659802</v>
       </c>
       <c r="P43" s="194">
         <f>SUM(P36:P42)</f>
@@ -24566,11 +24569,11 @@
       </c>
       <c r="R43" s="192">
         <f>SUM(R36:R42)</f>
-        <v>2.9846725714285718</v>
+        <v>2.9198205714285717</v>
       </c>
       <c r="S43" s="193">
         <f t="shared" si="8"/>
-        <v>1.9690767410814602</v>
+        <v>1.92629195924809</v>
       </c>
       <c r="T43" s="195">
         <f>SUM(T36:T42)</f>
@@ -24582,11 +24585,11 @@
       </c>
       <c r="V43" s="192">
         <f>SUM(V36:V42)</f>
-        <v>1.3154152380952382</v>
+        <v>1.3182723809523809</v>
       </c>
       <c r="W43" s="193">
         <f t="shared" si="9"/>
-        <v>0.70343060860707929</v>
+        <v>0.70495849248790421</v>
       </c>
       <c r="X43" s="194">
         <f>SUM(X36:X42)</f>
@@ -24598,11 +24601,11 @@
       </c>
       <c r="Z43" s="192">
         <f>SUM(Z36:Z42)</f>
-        <v>4.1081906857142858</v>
+        <v>4.1224764</v>
       </c>
       <c r="AA43" s="193">
         <f t="shared" si="10"/>
-        <v>0.96500494617582055</v>
+        <v>0.9683606290055653</v>
       </c>
       <c r="AB43" s="194">
         <f>SUM(AB36:AB42)</f>
@@ -24614,11 +24617,11 @@
       </c>
       <c r="AD43" s="192">
         <f>SUM(AD36:AD42)</f>
-        <v>3.6045581714285708</v>
+        <v>3.7617804523809517</v>
       </c>
       <c r="AE43" s="193">
         <f t="shared" si="11"/>
-        <v>0.34592688785302977</v>
+        <v>0.36101539850105097</v>
       </c>
       <c r="AF43" s="194">
         <f>SUM(AF36:AF42)</f>
@@ -24630,11 +24633,11 @@
       </c>
       <c r="AH43" s="192">
         <f>SUM(AH36:AH42)</f>
-        <v>2.5289088571428571</v>
+        <v>2.5431945714285713</v>
       </c>
       <c r="AI43" s="193">
         <f t="shared" si="12"/>
-        <v>0.25674201595358959</v>
+        <v>0.25819234227701232</v>
       </c>
       <c r="AJ43" s="197">
         <f>SUM(AJ36:AJ42)</f>
@@ -24683,7 +24686,7 @@
       </c>
       <c r="R45" s="112">
         <f>N27-R43</f>
-        <v>11.698044352380954</v>
+        <v>12.180002042857142</v>
       </c>
       <c r="S45" s="158"/>
       <c r="T45" s="112"/>
@@ -24846,7 +24849,7 @@
       </c>
       <c r="Y53" s="169">
         <f>'[4]Project Summary'!$L$18</f>
-        <v>0.57053149047619045</v>
+        <v>0.56077619999999995</v>
       </c>
       <c r="Z53" s="169">
         <f>'[5]Project Summary'!$L$18</f>
@@ -24858,11 +24861,11 @@
       </c>
       <c r="AB53" s="169">
         <f>'[7]Project Summary'!$L$18</f>
-        <v>0.96932516190476192</v>
+        <v>0.83242155238095239</v>
       </c>
       <c r="AC53" s="169">
         <f>SUM(V53:AB53)</f>
-        <v>7.3049516523809528</v>
+        <v>7.1582927523809534</v>
       </c>
     </row>
     <row r="54" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -24906,11 +24909,11 @@
       </c>
       <c r="Z54" s="169">
         <f>'[5]Project Summary'!$L$19</f>
-        <v>0.17557714285714288</v>
+        <v>0.1708152380952381</v>
       </c>
       <c r="AA54" s="169">
         <f>'[6]Project Summary'!$L$19</f>
-        <v>0.14353640000000001</v>
+        <v>0.36849140000000002</v>
       </c>
       <c r="AB54" s="169">
         <f>'[7]Project Summary'!$L$19</f>
@@ -24918,7 +24921,7 @@
       </c>
       <c r="AC54" s="169">
         <f>SUM(V54:AB54)</f>
-        <v>0.93128431428571423</v>
+        <v>1.1514774095238094</v>
       </c>
     </row>
     <row r="55" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -25029,11 +25032,11 @@
       </c>
       <c r="AB56" s="169">
         <f>'[7]Project Summary'!$L$21</f>
-        <v>0</v>
+        <v>0.16946637142857127</v>
       </c>
       <c r="AC56" s="169">
         <f>SUM(V56:AB56)</f>
-        <v>0.24146239523809523</v>
+        <v>0.4109287666666665</v>
       </c>
     </row>
     <row r="57" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -25064,7 +25067,7 @@
       </c>
       <c r="V57" s="168">
         <f>'[1]Project Summary'!$L$22</f>
-        <v>1.28019E-2</v>
+        <v>0.1128019</v>
       </c>
       <c r="W57" s="169">
         <f>'[2]Project Summary'!$L$22</f>
@@ -25072,11 +25075,11 @@
       </c>
       <c r="X57" s="169">
         <f>'[3]Project Summary'!$M$22</f>
-        <v>0.11251811428571427</v>
+        <v>1.0228971428571456E-2</v>
       </c>
       <c r="Y57" s="169">
         <f>'[4]Project Summary'!$L$22</f>
-        <v>0.12945950000000001</v>
+        <v>2.9171200000000001E-2</v>
       </c>
       <c r="Z57" s="169">
         <f>'[5]Project Summary'!$L$22</f>
@@ -25084,7 +25087,7 @@
       </c>
       <c r="AA57" s="169">
         <f>'[6]Project Summary'!$L$22</f>
-        <v>0.34916540000000001</v>
+        <v>0.3327928</v>
       </c>
       <c r="AB57" s="169">
         <f>'[7]Project Summary'!$L$22</f>
@@ -25092,7 +25095,7 @@
       </c>
       <c r="AC57" s="169">
         <f>SUM(V57:AB57)</f>
-        <v>2.2514050904761902</v>
+        <v>2.1324550476190476</v>
       </c>
     </row>
     <row r="58" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -25120,7 +25123,7 @@
       </c>
       <c r="V58" s="167">
         <f t="shared" ref="V58:AC58" si="14">SUM(V53:V57)</f>
-        <v>0.91047889999999998</v>
+        <v>1.0104788999999998</v>
       </c>
       <c r="W58" s="167">
         <f t="shared" si="14"/>
@@ -25128,27 +25131,27 @@
       </c>
       <c r="X58" s="167">
         <f t="shared" si="14"/>
-        <v>0.9739284476190474</v>
+        <v>0.87163930476190465</v>
       </c>
       <c r="Y58" s="167">
         <f t="shared" si="14"/>
-        <v>0.71522916190476193</v>
+        <v>0.60518557142857132</v>
       </c>
       <c r="Z58" s="167">
         <f t="shared" si="14"/>
-        <v>1.8145476285714284</v>
+        <v>1.8097857238095236</v>
       </c>
       <c r="AA58" s="167">
         <f t="shared" si="14"/>
-        <v>0.82184729999999995</v>
+        <v>1.0304297</v>
       </c>
       <c r="AB58" s="167">
         <f t="shared" si="14"/>
-        <v>2.6420232619047619</v>
+        <v>2.6745860238095238</v>
       </c>
       <c r="AC58" s="167">
         <f t="shared" si="14"/>
-        <v>10.729103452380953</v>
+        <v>10.853153976190477</v>
       </c>
     </row>
     <row r="59" spans="12:29" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -25473,11 +25476,11 @@
       </c>
       <c r="D2" s="217">
         <f>Overall_Draft!N20</f>
-        <v>0.68969819999999993</v>
+        <v>0.58969820000000006</v>
       </c>
       <c r="E2" s="218">
         <f t="shared" ref="E2:E9" si="0">IFERROR(D2/C2,"")</f>
-        <v>0.23618370517210788</v>
+        <v>0.20193920443655317</v>
       </c>
       <c r="F2" s="217">
         <f>Overall_Draft!P20</f>
@@ -25485,7 +25488,7 @@
       </c>
       <c r="G2" s="217">
         <f>Overall_Draft!Q20</f>
-        <v>1.0303018000000002</v>
+        <v>1.1303017999999998</v>
       </c>
       <c r="H2" s="219" t="str">
         <f>Overall_Draft!L4</f>
@@ -25493,7 +25496,7 @@
       </c>
       <c r="I2" s="219">
         <f>Overall_Draft!M4</f>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J2" s="205">
         <f ca="1">Overall_Draft!N4</f>
@@ -25501,7 +25504,7 @@
       </c>
       <c r="K2" s="205">
         <f>Overall_Draft!O4</f>
-        <v>1.0896982</v>
+        <v>0.98969819999999997</v>
       </c>
       <c r="L2" s="219">
         <f>Overall_Draft!P4</f>
@@ -25513,11 +25516,11 @@
       </c>
       <c r="N2" s="205">
         <f>Overall_Draft!R4</f>
-        <v>209.5071714</v>
+        <v>209.40717140000001</v>
       </c>
       <c r="O2" s="205">
         <f>Overall_Draft!S4</f>
-        <v>0.91047889999999998</v>
+        <v>1.0104789000000001</v>
       </c>
       <c r="P2" s="219">
         <f>Overall_Draft!T4</f>
@@ -25611,11 +25614,11 @@
       </c>
       <c r="AM2" s="205">
         <f>Overall_Draft!AD36</f>
-        <v>0.57719810000000005</v>
+        <v>0.47719810000000001</v>
       </c>
       <c r="AN2" s="206">
         <f>Overall_Draft!AE36</f>
-        <v>0.38225039735099342</v>
+        <v>0.31602523178807945</v>
       </c>
       <c r="AO2" s="205">
         <f>Overall_Draft!AF36</f>
@@ -25648,11 +25651,11 @@
       </c>
       <c r="AX2" s="205">
         <f>Overall!U20</f>
-        <v>4.4377010095238099</v>
+        <v>4.6690129904761903</v>
       </c>
       <c r="AY2" s="206">
         <f>Overall!V20</f>
-        <v>0.38303105484821071</v>
+        <v>0.40299627374715741</v>
       </c>
       <c r="AZ2" s="205">
         <f>Overall!W20</f>
@@ -25850,11 +25853,11 @@
       </c>
       <c r="AX3" s="209">
         <f>Overall!U21</f>
-        <v>2.4396125714285715</v>
+        <v>2.3747605714285718</v>
       </c>
       <c r="AY3" s="210">
         <f>Overall!V21</f>
-        <v>2.6872072821538473</v>
+        <v>2.6157734943863935</v>
       </c>
       <c r="AZ3" s="209">
         <f>Overall!W21</f>
@@ -25877,11 +25880,11 @@
       </c>
       <c r="D4" s="221">
         <f>Overall_Draft!N22</f>
-        <v>1.8337344476190478</v>
+        <v>1.9769759904761905</v>
       </c>
       <c r="E4" s="222">
         <f t="shared" si="0"/>
-        <v>0.34754335371103784</v>
+        <v>0.37469158461216606</v>
       </c>
       <c r="F4" s="221">
         <f>Overall_Draft!P22</f>
@@ -25889,7 +25892,7 @@
       </c>
       <c r="G4" s="221">
         <f>Overall_Draft!Q22</f>
-        <v>2.5765362523809521</v>
+        <v>2.4332947095238096</v>
       </c>
       <c r="H4" s="123" t="str">
         <f>Overall_Draft!L6</f>
@@ -25901,15 +25904,15 @@
       </c>
       <c r="J4" s="209">
         <f ca="1">Overall_Draft!N6</f>
-        <v>0</v>
+        <v>4.09524E-2</v>
       </c>
       <c r="K4" s="209">
         <f>Overall_Draft!O6</f>
-        <v>2.8276393047619064</v>
+        <v>3.0213570380952395</v>
       </c>
       <c r="L4" s="123">
         <f>Overall_Draft!P6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="209">
         <f>Overall_Draft!Q6</f>
@@ -25917,19 +25920,19 @@
       </c>
       <c r="N4" s="209">
         <f>Overall_Draft!R6</f>
-        <v>54.324063104761898</v>
+        <v>54.517780838095234</v>
       </c>
       <c r="O4" s="209">
         <f>Overall_Draft!S6</f>
-        <v>0.9739284476190474</v>
+        <v>0.87163930476190465</v>
       </c>
       <c r="P4" s="123">
         <f>Overall_Draft!T6</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q4" s="123">
         <f ca="1">Overall_Draft!U6</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R4" s="123">
         <f>Overall_Draft!V6</f>
@@ -25951,11 +25954,11 @@
       </c>
       <c r="W4" s="209">
         <f>Overall_Draft!N38</f>
-        <v>5.2380866666666671E-2</v>
+        <v>9.3333266666666678E-2</v>
       </c>
       <c r="X4" s="210">
         <f>Overall_Draft!O38</f>
-        <v>6.0485660951570673E-2</v>
+        <v>0.10777454979940257</v>
       </c>
       <c r="Y4" s="209">
         <f>Overall_Draft!P38</f>
@@ -25967,11 +25970,11 @@
       </c>
       <c r="AA4" s="209">
         <f>Overall_Draft!R38</f>
-        <v>0.12380952380952381</v>
+        <v>0.17142857142857143</v>
       </c>
       <c r="AB4" s="210">
         <f>Overall_Draft!S38</f>
-        <v>3.4517427118775923</v>
+        <v>4.779336062599743</v>
       </c>
       <c r="AC4" s="209">
         <f>Overall_Draft!T38</f>
@@ -25983,11 +25986,11 @@
       </c>
       <c r="AE4" s="209">
         <f>Overall_Draft!V38</f>
-        <v>0.87009533333333344</v>
+        <v>0.87295247619047611</v>
       </c>
       <c r="AF4" s="210">
         <f>Overall_Draft!W38</f>
-        <v>1.2429933333333336</v>
+        <v>1.2470749659863944</v>
       </c>
       <c r="AG4" s="209">
         <f>Overall_Draft!X38</f>
@@ -26015,11 +26018,11 @@
       </c>
       <c r="AM4" s="209">
         <f>Overall_Draft!AD38</f>
-        <v>0.20457828571428571</v>
+        <v>0.30686742857142857</v>
       </c>
       <c r="AN4" s="210">
         <f>Overall_Draft!AE38</f>
-        <v>7.3854976792160909E-2</v>
+        <v>0.11078246518824136</v>
       </c>
       <c r="AO4" s="209">
         <f>Overall_Draft!AF38</f>
@@ -26052,11 +26055,11 @@
       </c>
       <c r="AX4" s="209">
         <f>Overall!U22</f>
-        <v>1.3154152380952382</v>
+        <v>1.3182723809523809</v>
       </c>
       <c r="AY4" s="210">
         <f>Overall!V22</f>
-        <v>1.019701734957549</v>
+        <v>1.0219165743816905</v>
       </c>
       <c r="AZ4" s="209">
         <f>Overall!W22</f>
@@ -26079,11 +26082,11 @@
       </c>
       <c r="D5" s="221">
         <f>Overall_Draft!N23</f>
-        <v>2.2993296238095242</v>
+        <v>2.5050992190476191</v>
       </c>
       <c r="E5" s="222">
         <f t="shared" si="0"/>
-        <v>0.28572075388021251</v>
+        <v>0.31129022563765768</v>
       </c>
       <c r="F5" s="221">
         <f>Overall_Draft!P23</f>
@@ -26091,7 +26094,7 @@
       </c>
       <c r="G5" s="221">
         <f>Overall_Draft!Q23</f>
-        <v>4.360670376190475</v>
+        <v>4.1549007809523797</v>
       </c>
       <c r="H5" s="123" t="str">
         <f>Overall_Draft!L7</f>
@@ -26103,11 +26106,11 @@
       </c>
       <c r="J5" s="209">
         <f ca="1">Overall_Draft!N7</f>
-        <v>0.10770914285714286</v>
+        <v>0.20576959523809524</v>
       </c>
       <c r="K5" s="209">
         <f>Overall_Draft!O7</f>
-        <v>2.900483433333334</v>
+        <v>3.1062530285714289</v>
       </c>
       <c r="L5" s="123">
         <f>Overall_Draft!P7</f>
@@ -26119,11 +26122,11 @@
       </c>
       <c r="N5" s="209">
         <f>Overall_Draft!R7</f>
-        <v>41.883763633333324</v>
+        <v>42.089533228571419</v>
       </c>
       <c r="O5" s="209">
         <f>Overall_Draft!S7</f>
-        <v>0.71522916190476193</v>
+        <v>0.60518557142857143</v>
       </c>
       <c r="P5" s="123">
         <f>Overall_Draft!T7</f>
@@ -26153,11 +26156,11 @@
       </c>
       <c r="W5" s="209">
         <f>Overall_Draft!N39</f>
-        <v>0.56955540952380956</v>
+        <v>0.63694146666666662</v>
       </c>
       <c r="X5" s="210">
         <f>Overall_Draft!O39</f>
-        <v>0.55977529544936588</v>
+        <v>0.6260042336976186</v>
       </c>
       <c r="Y5" s="209">
         <f>Overall_Draft!P39</f>
@@ -26169,11 +26172,11 @@
       </c>
       <c r="AA5" s="209">
         <f>Overall_Draft!R39</f>
-        <v>0.36874257142857148</v>
+        <v>0.25150961904761909</v>
       </c>
       <c r="AB5" s="210">
         <f>Overall_Draft!S39</f>
-        <v>1.4682258434796778</v>
+        <v>1.001438269356361</v>
       </c>
       <c r="AC5" s="209">
         <f>Overall_Draft!T39</f>
@@ -26217,11 +26220,11 @@
       </c>
       <c r="AM5" s="209">
         <f>Overall_Draft!AD39</f>
-        <v>1.0301343095238096</v>
+        <v>1.1685178476190476</v>
       </c>
       <c r="AN5" s="210">
         <f>Overall_Draft!AE39</f>
-        <v>1.4929482746721878</v>
+        <v>1.6935041269841271</v>
       </c>
       <c r="AO5" s="209">
         <f>Overall_Draft!AF39</f>
@@ -26254,11 +26257,11 @@
       </c>
       <c r="AX5" s="209">
         <f>Overall!U23</f>
-        <v>4.1081906857142858</v>
+        <v>4.1224764</v>
       </c>
       <c r="AY5" s="210">
         <f>Overall!V23</f>
-        <v>0.96500494617582055</v>
+        <v>0.9683606290055653</v>
       </c>
       <c r="AZ5" s="209">
         <f>Overall!W23</f>
@@ -26305,11 +26308,11 @@
       </c>
       <c r="J6" s="209">
         <f ca="1">Overall_Draft!N8</f>
-        <v>0</v>
+        <v>9.5238095238095247E-6</v>
       </c>
       <c r="K6" s="209">
         <f>Overall_Draft!O8</f>
-        <v>5.2190673904761926</v>
+        <v>5.2190769142857167</v>
       </c>
       <c r="L6" s="123">
         <f>Overall_Draft!P8</f>
@@ -26321,11 +26324,11 @@
       </c>
       <c r="N6" s="209">
         <f>Overall_Draft!R8</f>
-        <v>37.05116699047619</v>
+        <v>37.055928895238097</v>
       </c>
       <c r="O6" s="209">
         <f>Overall_Draft!S8</f>
-        <v>1.8145476285714284</v>
+        <v>1.8097857238095234</v>
       </c>
       <c r="P6" s="123">
         <f>Overall_Draft!T8</f>
@@ -26371,11 +26374,11 @@
       </c>
       <c r="AA6" s="209">
         <f>Overall_Draft!R40</f>
-        <v>0.99661000000000022</v>
+        <v>1.001371904761905</v>
       </c>
       <c r="AB6" s="210">
         <f>Overall_Draft!S40</f>
-        <v>2.4844622948114252</v>
+        <v>2.4963333103866607</v>
       </c>
       <c r="AC6" s="209">
         <f>Overall_Draft!T40</f>
@@ -26456,11 +26459,11 @@
       </c>
       <c r="AX6" s="209">
         <f>Overall!U24</f>
-        <v>3.2899397714285707</v>
+        <v>3.4306124523809518</v>
       </c>
       <c r="AY6" s="210">
         <f>Overall!V24</f>
-        <v>0.34740652285412571</v>
+        <v>0.36226108261678475</v>
       </c>
       <c r="AZ6" s="209">
         <f>Overall!W24</f>
@@ -26483,11 +26486,11 @@
       </c>
       <c r="D7" s="221">
         <f>Overall_Draft!N25</f>
-        <v>0.31797660000000005</v>
+        <v>0.3345262</v>
       </c>
       <c r="E7" s="222">
         <f t="shared" si="0"/>
-        <v>0.16932480917207343</v>
+        <v>0.17813758930078144</v>
       </c>
       <c r="F7" s="221">
         <f>Overall_Draft!P25</f>
@@ -26495,7 +26498,7 @@
       </c>
       <c r="G7" s="221">
         <f>Overall_Draft!Q25</f>
-        <v>1.3020233999999999</v>
+        <v>1.2854737999999999</v>
       </c>
       <c r="H7" s="123" t="str">
         <f>Overall_Draft!L9</f>
@@ -26503,15 +26506,15 @@
       </c>
       <c r="I7" s="123">
         <f>Overall_Draft!M9</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7" s="209">
-        <f ca="1">Overall_Draft!N9</f>
-        <v>0</v>
+        <f>Overall_Draft!N9</f>
+        <v>1.6549600000000001E-2</v>
       </c>
       <c r="K7" s="209">
         <f>Overall_Draft!O9</f>
-        <v>0.86303660000000004</v>
+        <v>0.87958619999999998</v>
       </c>
       <c r="L7" s="123">
         <f>Overall_Draft!P9</f>
@@ -26519,23 +26522,23 @@
       </c>
       <c r="M7" s="209">
         <f>Overall_Draft!Q9</f>
-        <v>3.8853399</v>
+        <v>4.1102949000000004</v>
       </c>
       <c r="N7" s="209">
         <f>Overall_Draft!R9</f>
-        <v>4.0258928999999997</v>
+        <v>4.0424424999999999</v>
       </c>
       <c r="O7" s="209">
         <f>Overall_Draft!S9</f>
-        <v>0.82184729999999995</v>
+        <v>1.0304297</v>
       </c>
       <c r="P7" s="123">
         <f>Overall_Draft!T9</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="123">
-        <f ca="1">Overall_Draft!U9</f>
-        <v>6</v>
+        <f>Overall_Draft!U9</f>
+        <v>7</v>
       </c>
       <c r="R7" s="123">
         <f>Overall_Draft!V9</f>
@@ -26621,11 +26624,11 @@
       </c>
       <c r="AM7" s="209">
         <f>Overall_Draft!AD41</f>
-        <v>0.31461840000000002</v>
+        <v>0.33116800000000002</v>
       </c>
       <c r="AN7" s="210">
         <f>Overall_Draft!AE41</f>
-        <v>0.33117726315789475</v>
+        <v>0.34859789473684216</v>
       </c>
       <c r="AO7" s="209">
         <f>Overall_Draft!AF41</f>
@@ -26658,11 +26661,11 @@
       </c>
       <c r="AX7" s="213">
         <f>Overall!U25</f>
-        <v>2.5289088571428571</v>
+        <v>2.5431945714285713</v>
       </c>
       <c r="AY7" s="214">
         <f>Overall!V25</f>
-        <v>0.27820779506522081</v>
+        <v>0.27977938079522235</v>
       </c>
       <c r="AZ7" s="213">
         <f>Overall!W25</f>
@@ -26685,11 +26688,11 @@
       </c>
       <c r="D8" s="221">
         <f>Overall_Draft!N26</f>
-        <v>5.1130300904761912</v>
+        <v>5.2645750428571434</v>
       </c>
       <c r="E8" s="222">
         <f t="shared" si="0"/>
-        <v>0.58045994095330022</v>
+        <v>0.59766417651504045</v>
       </c>
       <c r="F8" s="221">
         <f>Overall_Draft!P26</f>
@@ -26697,7 +26700,7 @@
       </c>
       <c r="G8" s="221">
         <f>Overall_Draft!Q26</f>
-        <v>2.66696990952381</v>
+        <v>2.5154249571428577</v>
       </c>
       <c r="H8" s="123" t="str">
         <f>Overall_Draft!L10</f>
@@ -26709,11 +26712,11 @@
       </c>
       <c r="J8" s="209">
         <f ca="1">Overall_Draft!N10</f>
-        <v>0.1</v>
+        <v>7.3509714285714289E-2</v>
       </c>
       <c r="K8" s="209">
         <f>Overall_Draft!O10</f>
-        <v>5.6634805666666672</v>
+        <v>5.8150255190476194</v>
       </c>
       <c r="L8" s="123">
         <f>Overall_Draft!P10</f>
@@ -26721,15 +26724,15 @@
       </c>
       <c r="M8" s="209">
         <f>Overall_Draft!Q10</f>
-        <v>30.033064599999999</v>
+        <v>30.226488</v>
       </c>
       <c r="N8" s="209">
         <f>Overall_Draft!R10</f>
-        <v>28.111590066666661</v>
+        <v>28.263135019047613</v>
       </c>
       <c r="O8" s="209">
         <f>Overall_Draft!S10</f>
-        <v>2.6420232619047619</v>
+        <v>2.6745860238095234</v>
       </c>
       <c r="P8" s="123">
         <f>Overall_Draft!T10</f>
@@ -26759,11 +26762,11 @@
       </c>
       <c r="W8" s="209">
         <f>Overall_Draft!N42</f>
-        <v>2.1237009571428573</v>
+        <v>2.2466744809523811</v>
       </c>
       <c r="X8" s="210">
         <f>Overall_Draft!O42</f>
-        <v>1.1073005717441535</v>
+        <v>1.1714191345604903</v>
       </c>
       <c r="Y8" s="209">
         <f>Overall_Draft!P42</f>
@@ -26807,11 +26810,11 @@
       </c>
       <c r="AI8" s="209">
         <f>Overall_Draft!Z42</f>
-        <v>1.4603469142857144</v>
+        <v>1.4746326285714286</v>
       </c>
       <c r="AJ8" s="210">
         <f>Overall_Draft!AA42</f>
-        <v>1.0066667656681578</v>
+        <v>1.0165143941012234</v>
       </c>
       <c r="AK8" s="209">
         <f>Overall_Draft!AB42</f>
@@ -26839,11 +26842,11 @@
       </c>
       <c r="AQ8" s="209">
         <f>Overall_Draft!AH42</f>
-        <v>1.5093696190476189</v>
+        <v>1.5236553333333331</v>
       </c>
       <c r="AR8" s="210">
         <f>Overall_Draft!AI42</f>
-        <v>0.57830253603357051</v>
+        <v>0.58377598978288625</v>
       </c>
       <c r="AS8" s="211">
         <f>Overall_Draft!AJ42</f>
@@ -26861,11 +26864,11 @@
       </c>
       <c r="D9" s="224">
         <f>Overall_Draft!N27</f>
-        <v>14.682716923809526</v>
+        <v>15.099822614285713</v>
       </c>
       <c r="E9" s="225">
         <f t="shared" si="0"/>
-        <v>0.40727822759265764</v>
+        <v>0.41884816163262256</v>
       </c>
       <c r="F9" s="224">
         <f>Overall_Draft!P27</f>
@@ -26873,7 +26876,7 @@
       </c>
       <c r="G9" s="224">
         <f>Overall_Draft!Q27</f>
-        <v>13.223778076190477</v>
+        <v>12.80667238571429</v>
       </c>
       <c r="H9" s="226" t="str">
         <f>Overall_Draft!L11</f>
@@ -26881,31 +26884,31 @@
       </c>
       <c r="I9" s="226">
         <f>Overall_Draft!M11</f>
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J9" s="213">
         <f ca="1">Overall_Draft!N11</f>
-        <v>0.20770914285714287</v>
+        <v>0.33679083333333337</v>
       </c>
       <c r="K9" s="213">
         <f>Overall_Draft!O11</f>
-        <v>18.856047971428577</v>
+        <v>19.323639376190481</v>
       </c>
       <c r="L9" s="226">
         <f>Overall_Draft!P11</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M9" s="213">
         <f>Overall_Draft!Q11</f>
-        <v>477.31268460000007</v>
+        <v>477.73106300000006</v>
       </c>
       <c r="N9" s="213">
         <f>Overall_Draft!R11</f>
-        <v>474.87915517142852</v>
+        <v>475.35149895714284</v>
       </c>
       <c r="O9" s="213">
         <f>Overall_Draft!S11</f>
-        <v>10.729103452380951</v>
+        <v>10.853153976190475</v>
       </c>
       <c r="P9" s="226">
         <f>Overall_Draft!T11</f>
@@ -26934,11 +26937,11 @@
       </c>
       <c r="W9" s="213">
         <f>Overall_Draft!N43</f>
-        <v>4.4410592095238099</v>
+        <v>4.6723711904761913</v>
       </c>
       <c r="X9" s="214">
         <f>Overall_Draft!O43</f>
-        <v>0.38538629193454693</v>
+        <v>0.40545908592659802</v>
       </c>
       <c r="Y9" s="213">
         <f>Overall_Draft!P43</f>
@@ -26950,11 +26953,11 @@
       </c>
       <c r="AA9" s="213">
         <f>Overall_Draft!R43</f>
-        <v>2.9846725714285718</v>
+        <v>2.9198205714285717</v>
       </c>
       <c r="AB9" s="214">
         <f>Overall_Draft!S43</f>
-        <v>1.9690767410814602</v>
+        <v>1.92629195924809</v>
       </c>
       <c r="AC9" s="213">
         <f>Overall_Draft!T43</f>
@@ -26966,11 +26969,11 @@
       </c>
       <c r="AE9" s="213">
         <f>Overall_Draft!V43</f>
-        <v>1.3154152380952382</v>
+        <v>1.3182723809523809</v>
       </c>
       <c r="AF9" s="214">
         <f>Overall_Draft!W43</f>
-        <v>0.70343060860707929</v>
+        <v>0.70495849248790421</v>
       </c>
       <c r="AG9" s="213">
         <f>Overall_Draft!X43</f>
@@ -26982,11 +26985,11 @@
       </c>
       <c r="AI9" s="213">
         <f>Overall_Draft!Z43</f>
-        <v>4.1081906857142858</v>
+        <v>4.1224764</v>
       </c>
       <c r="AJ9" s="214">
         <f>Overall_Draft!AA43</f>
-        <v>0.96500494617582055</v>
+        <v>0.9683606290055653</v>
       </c>
       <c r="AK9" s="213">
         <f>Overall_Draft!AB43</f>
@@ -26998,11 +27001,11 @@
       </c>
       <c r="AM9" s="213">
         <f>Overall_Draft!AD43</f>
-        <v>3.6045581714285708</v>
+        <v>3.7617804523809517</v>
       </c>
       <c r="AN9" s="214">
         <f>Overall_Draft!AE43</f>
-        <v>0.34592688785302977</v>
+        <v>0.36101539850105097</v>
       </c>
       <c r="AO9" s="213">
         <f>Overall_Draft!AF43</f>
@@ -27014,11 +27017,11 @@
       </c>
       <c r="AQ9" s="213">
         <f>Overall_Draft!AH43</f>
-        <v>2.5289088571428571</v>
+        <v>2.5431945714285713</v>
       </c>
       <c r="AR9" s="214">
         <f>Overall_Draft!AI43</f>
-        <v>0.25674201595358959</v>
+        <v>0.25819234227701232</v>
       </c>
       <c r="AS9" s="215">
         <f>Overall_Draft!AJ43</f>
@@ -27034,15 +27037,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="720fc211-b8f9-4216-8e59-f92e385e0bb9">
@@ -27064,6 +27058,15 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27244,26 +27247,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{037A7D67-D63F-48F5-85CA-5FAB13DF5982}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850BD086-9051-4567-AFD1-B7C8873D4F2D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="1c221b64-27b2-4021-9af7-79dcbf083a1e"/>
+    <ds:schemaRef ds:uri="720fc211-b8f9-4216-8e59-f92e385e0bb9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850BD086-9051-4567-AFD1-B7C8873D4F2D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{037A7D67-D63F-48F5-85CA-5FAB13DF5982}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="720fc211-b8f9-4216-8e59-f92e385e0bb9"/>
-    <ds:schemaRef ds:uri="1c221b64-27b2-4021-9af7-79dcbf083a1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/Overall Collection Summary - June 2026.xlsx
+++ b/data/Overall Collection Summary - June 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://raghavgroup.sharepoint.com/sites/CRM/Shared Documents/General/LAKSHYA TRACKERS MONTHLY/LAKSHYA CRM TRACKER/LAKSHYA CRM Tracker - June'26/Overall Summary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10342" documentId="8_{AED7C0B6-5B33-4314-A282-567B12F8F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24FC90DF-7D50-48C1-A65B-19765C6D2FC4}"/>
+  <xr:revisionPtr revIDLastSave="10355" documentId="8_{AED7C0B6-5B33-4314-A282-567B12F8F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DAC75E6-45CA-438B-A1B5-CDE1CEEBF13C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="917" firstSheet="2" activeTab="2" xr2:uid="{3D2F352B-9E05-401C-B527-666CFC22F994}"/>
   </bookViews>
@@ -2453,6 +2453,15 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2466,15 +2475,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3167,7 +3167,7 @@
                   <c:v>2.756608838095238</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.137677390476191</c:v>
+                  <c:v>5.3522784380952384</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -3488,7 +3488,7 @@
                         <c:v>0.33217678015295515</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.8000684493091238</c:v>
+                        <c:v>0.83348734939556357</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -3523,7 +3523,7 @@
                           <c:extLst>
                             <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                              <c16:uniqueId val="{00000002-8577-49EE-B700-0CF398B37908}"/>
+                              <c16:uniqueId val="{00000002-4ECC-4953-8EAD-3634F34760C3}"/>
                             </c:ext>
                           </c:extLst>
                         </c15:dLbl>
@@ -4260,16 +4260,16 @@
                   <c:v>4.6690129904761903</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3747605714285718</c:v>
+                  <c:v>2.4223796190476197</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.3182723809523809</c:v>
+                  <c:v>1.7007692380952382</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4.1224764</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.4306124523809518</c:v>
+                  <c:v>3.5975944523809518</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2.5431945714285713</c:v>
@@ -4441,16 +4441,16 @@
                         <c:v>0.40299627374715741</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>2.6157734943863935</c:v>
+                        <c:v>2.6682253685199186</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>1.0219165743816905</c:v>
+                        <c:v>1.3184257659653009</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0.9683606290055653</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.36226108261678475</c:v>
+                        <c:v>0.37989381756926627</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0.27977938079522235</c:v>
@@ -7076,10 +7076,10 @@
                   <c:v>2.5050992190476191</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.1363054857142858</c:v>
+                  <c:v>4.3032874857142858</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3345262</c:v>
+                  <c:v>0.51571670000000014</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>5.2645750428571434</c:v>
@@ -7397,10 +7397,10 @@
                         <c:v>0.31129022563765768</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.68704711943287278</c:v>
+                        <c:v>0.7147831032699874</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0.17813758930078144</c:v>
+                        <c:v>0.27462282386298692</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0.64682710218888106</c:v>
@@ -7432,7 +7432,7 @@
                           <c:extLst>
                             <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                              <c16:uniqueId val="{00000002-DFEF-4440-B9D8-A914BD041D6F}"/>
+                              <c16:uniqueId val="{00000002-3FEB-4272-ADDA-81104DD1B290}"/>
                             </c:ext>
                           </c:extLst>
                         </c15:dLbl>
@@ -8234,19 +8234,19 @@
                 <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.6723711904761913</c:v>
+                  <c:v>4.8369220904761914</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.9198205714285717</c:v>
+                  <c:v>3.1423946190476197</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.3182723809523809</c:v>
+                  <c:v>1.7007692380952382</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4.1224764</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.7617804523809517</c:v>
+                  <c:v>3.9454020523809517</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2.5431945714285713</c:v>
@@ -8416,19 +8416,19 @@
                       <c:formatCode>0.00%</c:formatCode>
                       <c:ptCount val="6"/>
                       <c:pt idx="0">
-                        <c:v>0.40545908592659802</c:v>
+                        <c:v>0.41973848599618013</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>1.92629195924809</c:v>
+                        <c:v>2.0731306391523501</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.70495849248790421</c:v>
+                        <c:v>0.90950226636108999</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0.9683606290055653</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0.36101539850105097</c:v>
+                        <c:v>0.37863743304999531</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0.25819234227701232</c:v>
@@ -17533,10 +17533,10 @@
         </row>
         <row r="21">
           <cell r="D21">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="F21">
-            <v>3</v>
+            <v>2</v>
           </cell>
           <cell r="I21">
             <v>4.8954400000000002E-2</v>
@@ -17604,6 +17604,10 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6">
+        <row r="3">
+          <cell r="Q3"/>
+          <cell r="R3"/>
+        </row>
         <row r="7">
           <cell r="B7">
             <v>105</v>
@@ -17634,26 +17638,35 @@
           <cell r="J8">
             <v>0</v>
           </cell>
+          <cell r="L8"/>
         </row>
         <row r="9">
+          <cell r="I9"/>
           <cell r="J9">
             <v>0</v>
           </cell>
+          <cell r="L9"/>
         </row>
         <row r="10">
+          <cell r="I10"/>
           <cell r="J10">
             <v>0</v>
           </cell>
+          <cell r="L10"/>
         </row>
         <row r="11">
+          <cell r="I11"/>
           <cell r="J11">
             <v>0</v>
           </cell>
+          <cell r="L11"/>
         </row>
         <row r="12">
+          <cell r="I12"/>
           <cell r="J12">
             <v>0</v>
           </cell>
+          <cell r="L12"/>
         </row>
         <row r="13">
           <cell r="C13">
@@ -17744,12 +17757,12 @@
       <sheetName val="Slots"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="3">
           <cell r="Q3">
@@ -17764,10 +17777,10 @@
             <v>87</v>
           </cell>
           <cell r="D7">
-            <v>4.09524E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E7">
-            <v>3.0213570380952395</v>
+            <v>3.1236478952380966</v>
           </cell>
           <cell r="F7">
             <v>2</v>
@@ -17792,7 +17805,7 @@
             <v>0.7</v>
           </cell>
           <cell r="J9">
-            <v>0.87295247619047611</v>
+            <v>0.97524333333333335</v>
           </cell>
           <cell r="L9">
             <v>0.7</v>
@@ -17836,7 +17849,7 @@
             <v>53.942062300000003</v>
           </cell>
           <cell r="D13">
-            <v>54.517780838095234</v>
+            <v>54.620071695238089</v>
           </cell>
           <cell r="E13">
             <v>0.87163930476190465</v>
@@ -17883,13 +17896,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -17938,7 +17951,7 @@
             <v>59</v>
           </cell>
           <cell r="D7">
-            <v>0.20576959523809524</v>
+            <v>0</v>
           </cell>
           <cell r="E7">
             <v>3.1062530285714289</v>
@@ -18115,16 +18128,16 @@
         </row>
         <row r="7">
           <cell r="B7">
-            <v>57</v>
+            <v>59</v>
           </cell>
           <cell r="D7">
-            <v>9.5238095238095247E-6</v>
+            <v>0</v>
           </cell>
           <cell r="E7">
-            <v>5.2190769142857167</v>
+            <v>5.5354573904761928</v>
           </cell>
           <cell r="F7">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="I7">
             <v>3.0441859</v>
@@ -18141,7 +18154,7 @@
             <v>0.40113710000000002</v>
           </cell>
           <cell r="J8">
-            <v>1.001371904761905</v>
+            <v>1.0489909523809526</v>
           </cell>
         </row>
         <row r="9">
@@ -18149,7 +18162,7 @@
             <v>0.09</v>
           </cell>
           <cell r="J9">
-            <v>8.6151904761904763E-2</v>
+            <v>0.36635790476190477</v>
           </cell>
         </row>
         <row r="10">
@@ -18168,7 +18181,7 @@
             <v>1.67</v>
           </cell>
           <cell r="J11">
-            <v>1.4584164761904759</v>
+            <v>1.6253984761904758</v>
           </cell>
           <cell r="L11">
             <v>1.67</v>
@@ -18190,16 +18203,16 @@
             <v>36.256671900000001</v>
           </cell>
           <cell r="D13">
-            <v>37.055928895238097</v>
+            <v>37.550735942857152</v>
           </cell>
           <cell r="E13">
-            <v>1.8097857238095234</v>
+            <v>1.7621666761904762</v>
           </cell>
           <cell r="I13">
             <v>6.4215473000000003</v>
           </cell>
           <cell r="J13">
-            <v>5.137677390476191</v>
+            <v>5.3522784380952384</v>
           </cell>
           <cell r="L13">
             <v>5.2162243000000004</v>
@@ -18212,12 +18225,12 @@
         </row>
         <row r="19">
           <cell r="L19">
-            <v>0.1708152380952381</v>
+            <v>0.12319619047619046</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="F20">
             <v>3</v>
@@ -18292,10 +18305,10 @@
             <v>18</v>
           </cell>
           <cell r="D7">
-            <v>1.6549600000000001E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E7">
-            <v>0.87958619999999998</v>
+            <v>1.2357317000000001</v>
           </cell>
           <cell r="F7">
             <v>8</v>
@@ -18304,7 +18317,7 @@
             <v>0.16790910000000001</v>
           </cell>
           <cell r="J7">
-            <v>3.3582E-3</v>
+            <v>0.16790910000000001</v>
           </cell>
           <cell r="L7">
             <v>0.17</v>
@@ -18315,7 +18328,7 @@
             <v>0.60791090000000003</v>
           </cell>
           <cell r="J8">
-            <v>0.54505999999999999</v>
+            <v>0.72001499999999996</v>
           </cell>
         </row>
         <row r="9">
@@ -18336,7 +18349,7 @@
             <v>0.95</v>
           </cell>
           <cell r="J11">
-            <v>0.33116800000000002</v>
+            <v>0.34780759999999999</v>
           </cell>
           <cell r="L11">
             <v>0.95</v>
@@ -18358,16 +18371,16 @@
             <v>4.1102949000000004</v>
           </cell>
           <cell r="D13">
-            <v>4.0424424999999999</v>
+            <v>4.3985880000000002</v>
           </cell>
           <cell r="E13">
-            <v>1.0304297</v>
+            <v>0.6742842</v>
           </cell>
           <cell r="I13">
             <v>2.4858199999999995</v>
           </cell>
           <cell r="J13">
-            <v>0.87958619999999998</v>
+            <v>1.2357317000000001</v>
           </cell>
           <cell r="L13">
             <v>1.6199999999999999</v>
@@ -18378,7 +18391,7 @@
             <v>0</v>
           </cell>
           <cell r="L18">
-            <v>0.32914549999999998</v>
+            <v>0.16459460000000001</v>
           </cell>
         </row>
         <row r="19">
@@ -18386,7 +18399,7 @@
             <v>0</v>
           </cell>
           <cell r="L19">
-            <v>0.36849140000000002</v>
+            <v>0.1935364</v>
           </cell>
         </row>
         <row r="20">
@@ -18416,7 +18429,7 @@
             <v>0</v>
           </cell>
           <cell r="L22">
-            <v>0.3327928</v>
+            <v>0.31615320000000002</v>
           </cell>
         </row>
         <row r="23">
@@ -18475,7 +18488,7 @@
             <v>26</v>
           </cell>
           <cell r="D7">
-            <v>7.3509714285714289E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E7">
             <v>5.8150255190476194</v>
@@ -18974,7 +18987,7 @@
       <c r="H1" s="97"/>
       <c r="I1" s="98">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="L1" s="110"/>
       <c r="M1" s="110" t="s">
@@ -19003,16 +19016,16 @@
     <row r="3" spans="2:32" ht="134.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="100" t="str">
         <f>CONCATENATE("₹ ",ROUND($N$27,2)," / ",ROUND($M$27,2)," (",ROUND($O$27,3)*100,"%)")</f>
-        <v>₹ 17.14 / 35.31 (48.5%)</v>
+        <v>₹ 17.35 / 35.31 (49.1%)</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="85" t="str">
         <f ca="1">CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
-        <v>₹ 0.32  |  ₹ 18.44</v>
+        <v>₹ 0  |  ₹ 18.86</v>
       </c>
       <c r="G3" s="244" t="str">
         <f ca="1">CONCATENATE($U$11, "    |    ", $T$11)</f>
-        <v>24    |    42</v>
+        <v>23    |    42</v>
       </c>
       <c r="H3" s="245"/>
       <c r="I3" s="246"/>
@@ -19104,11 +19117,11 @@
       </c>
       <c r="T4" s="69">
         <f>'[1]Project Summary'!$D$21</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U4" s="69">
         <f ca="1">'[1]Project Summary'!$F$21</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V4" s="69">
         <f>'[1]Project Summary'!$Q$3</f>
@@ -19134,7 +19147,7 @@
         <v>105</v>
       </c>
       <c r="N5" s="102">
-        <f ca="1">'[2]Project Summary'!$D$7</f>
+        <f>'[2]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O5" s="102">
@@ -19162,7 +19175,7 @@
         <v>1</v>
       </c>
       <c r="U5" s="69">
-        <f ca="1">'[2]Project Summary'!$F$20</f>
+        <f>'[2]Project Summary'!$F$20</f>
         <v>1</v>
       </c>
       <c r="V5" s="69">
@@ -19185,7 +19198,7 @@
     <row r="6" spans="2:32" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="84">
         <f>$S$11</f>
-        <v>10.051579776190476</v>
+        <v>10.003960728571428</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="9"/>
@@ -19195,7 +19208,7 @@
       </c>
       <c r="G6" s="250" t="str">
         <f>CONCATENATE($P$11," / ",V11)</f>
-        <v>12 / 18</v>
+        <v>13 / 18</v>
       </c>
       <c r="H6" s="251"/>
       <c r="I6" s="252"/>
@@ -19207,12 +19220,12 @@
         <v>87</v>
       </c>
       <c r="N6" s="102">
-        <f ca="1">'[3]Project Summary'!$D$7</f>
-        <v>4.09524E-2</v>
+        <f>'[3]Project Summary'!$D$7</f>
+        <v>0</v>
       </c>
       <c r="O6" s="102">
         <f>'[3]Project Summary'!$E$7</f>
-        <v>3.0213570380952395</v>
+        <v>3.1236478952380966</v>
       </c>
       <c r="P6" s="105">
         <f>'[3]Project Summary'!$F$7</f>
@@ -19224,7 +19237,7 @@
       </c>
       <c r="R6" s="82">
         <f>'[3]Project Summary'!$D$13</f>
-        <v>54.517780838095234</v>
+        <v>54.620071695238089</v>
       </c>
       <c r="S6" s="82">
         <f>'[3]Project Summary'!$E$13</f>
@@ -19235,7 +19248,7 @@
         <v>23</v>
       </c>
       <c r="U6" s="69">
-        <f ca="1">'[3]Project Summary'!$F$20</f>
+        <f>'[3]Project Summary'!$F$20</f>
         <v>11</v>
       </c>
       <c r="V6" s="69">
@@ -19275,7 +19288,7 @@
       </c>
       <c r="N7" s="102">
         <f ca="1">'[4]Project Summary'!$D$7</f>
-        <v>0.20576959523809524</v>
+        <v>0</v>
       </c>
       <c r="O7" s="102">
         <f>'[4]Project Summary'!$E$7</f>
@@ -19326,19 +19339,19 @@
       </c>
       <c r="M8" s="69">
         <f>'[5]Project Summary'!$B$7</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N8" s="102">
         <f ca="1">'[5]Project Summary'!$D$7</f>
-        <v>9.5238095238095247E-6</v>
+        <v>0</v>
       </c>
       <c r="O8" s="102">
         <f>'[5]Project Summary'!$E$7</f>
-        <v>5.2190769142857167</v>
+        <v>5.5354573904761928</v>
       </c>
       <c r="P8" s="105">
         <f>'[5]Project Summary'!$F$7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="82">
         <f>'[5]Project Summary'!$C$13</f>
@@ -19346,15 +19359,15 @@
       </c>
       <c r="R8" s="82">
         <f>'[5]Project Summary'!$D$13</f>
-        <v>37.055928895238097</v>
+        <v>37.550735942857152</v>
       </c>
       <c r="S8" s="82">
         <f>'[5]Project Summary'!$E$13</f>
-        <v>1.8097857238095234</v>
+        <v>1.7621666761904762</v>
       </c>
       <c r="T8" s="69">
         <f>'[5]Project Summary'!$D$20</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8" s="69">
         <f ca="1">'[5]Project Summary'!$F$20</f>
@@ -19426,7 +19439,7 @@
       </c>
       <c r="N10" s="102">
         <f ca="1">'[7]Project Summary'!$D$7</f>
-        <v>7.3509714285714289E-2</v>
+        <v>0</v>
       </c>
       <c r="O10" s="103">
         <f>'[7]Project Summary'!$E$7</f>
@@ -19476,19 +19489,19 @@
       </c>
       <c r="M11" s="117">
         <f>SUM(M4:M10)</f>
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N11" s="118">
         <f t="shared" ref="N11:W11" ca="1" si="0">SUM(N4:N10)</f>
-        <v>0.32024123333333332</v>
+        <v>0</v>
       </c>
       <c r="O11" s="118">
         <f>SUM(O4:O10)</f>
-        <v>18.444053176190479</v>
+        <v>18.862724509523815</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q11" s="120">
         <f t="shared" si="0"/>
@@ -19496,11 +19509,11 @@
       </c>
       <c r="R11" s="120">
         <f t="shared" si="0"/>
-        <v>549.66679305714274</v>
+        <v>550.26389096190474</v>
       </c>
       <c r="S11" s="120">
         <f t="shared" si="0"/>
-        <v>10.051579776190476</v>
+        <v>10.003960728571428</v>
       </c>
       <c r="T11" s="121">
         <f t="shared" si="0"/>
@@ -19508,7 +19521,7 @@
       </c>
       <c r="U11" s="121">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V11" s="121">
         <f t="shared" si="0"/>
@@ -19685,11 +19698,11 @@
       </c>
       <c r="U21" s="64">
         <f>R43</f>
-        <v>2.3747605714285718</v>
+        <v>2.4223796190476197</v>
       </c>
       <c r="V21" s="88">
         <f>S43</f>
-        <v>2.6157734943863935</v>
+        <v>2.6682253685199186</v>
       </c>
       <c r="W21" s="64">
         <f>T43</f>
@@ -19734,11 +19747,11 @@
       </c>
       <c r="U22" s="64">
         <f>V43</f>
-        <v>1.3182723809523809</v>
+        <v>1.7007692380952382</v>
       </c>
       <c r="V22" s="88">
         <f>W43</f>
-        <v>1.0219165743816905</v>
+        <v>1.3184257659653009</v>
       </c>
       <c r="W22" s="64">
         <f>X43</f>
@@ -19812,11 +19825,11 @@
       </c>
       <c r="N24" s="18">
         <f>'[5]Project Summary'!$J$13</f>
-        <v>5.137677390476191</v>
+        <v>5.3522784380952384</v>
       </c>
       <c r="O24" s="19">
         <f>N24/M24</f>
-        <v>0.8000684493091238</v>
+        <v>0.83348734939556357</v>
       </c>
       <c r="P24" s="18">
         <f>'[5]Project Summary'!$L$13</f>
@@ -19838,11 +19851,11 @@
       </c>
       <c r="U24" s="64">
         <f>AD43</f>
-        <v>3.4306124523809518</v>
+        <v>3.5975944523809518</v>
       </c>
       <c r="V24" s="88">
         <f>AE43</f>
-        <v>0.36226108261678475</v>
+        <v>0.37989381756926627</v>
       </c>
       <c r="W24" s="64">
         <f>AF43</f>
@@ -19936,11 +19949,11 @@
       </c>
       <c r="N27" s="18">
         <f>SUM(N20:N26)</f>
-        <v>17.140056985714288</v>
+        <v>17.354658033333337</v>
       </c>
       <c r="O27" s="19">
         <f>N27/M27</f>
-        <v>0.48540579335479433</v>
+        <v>0.49148328725467549</v>
       </c>
       <c r="P27" s="18">
         <f>SUM(P20:P26)</f>
@@ -19948,7 +19961,7 @@
       </c>
       <c r="Q27" s="153">
         <f t="shared" si="2"/>
-        <v>18.170722614285715</v>
+        <v>17.956121566666667</v>
       </c>
       <c r="AF27" s="1"/>
     </row>
@@ -20018,7 +20031,7 @@
       <c r="AB34" s="237"/>
       <c r="AC34" s="232" t="str">
         <f ca="1">CONCATENATE("Expected Registrations in August ",$D$3,"'",$E$3," ")</f>
-        <v xml:space="preserve">Expected Registrations in August '₹ 0.32  |  ₹ 18.44 </v>
+        <v xml:space="preserve">Expected Registrations in August '₹ 0  |  ₹ 18.86 </v>
       </c>
       <c r="AD34" s="233"/>
       <c r="AE34" s="233"/>
@@ -20365,11 +20378,11 @@
       </c>
       <c r="V38" s="63">
         <f>'[3]Project Summary'!$J$9</f>
-        <v>0.87295247619047611</v>
+        <v>0.97524333333333335</v>
       </c>
       <c r="W38" s="88">
         <f t="shared" si="6"/>
-        <v>1.2470749659863944</v>
+        <v>1.3932047619047621</v>
       </c>
       <c r="X38" s="146">
         <f>'[3]Project Summary'!$L$9</f>
@@ -20557,11 +20570,11 @@
       </c>
       <c r="R40" s="63">
         <f>'[5]Project Summary'!$J$8</f>
-        <v>1.001371904761905</v>
+        <v>1.0489909523809526</v>
       </c>
       <c r="S40" s="88">
         <f t="shared" si="5"/>
-        <v>2.4963333103866607</v>
+        <v>2.6150434661390149</v>
       </c>
       <c r="T40" s="124">
         <f>'[5]Project Summary'!$L$8</f>
@@ -20573,11 +20586,11 @@
       </c>
       <c r="V40" s="63">
         <f>'[5]Project Summary'!$J$9</f>
-        <v>8.6151904761904763E-2</v>
+        <v>0.36635790476190477</v>
       </c>
       <c r="W40" s="88">
         <f t="shared" si="6"/>
-        <v>0.95724338624338634</v>
+        <v>4.0706433862433862</v>
       </c>
       <c r="X40" s="146">
         <f>'[5]Project Summary'!$L$9</f>
@@ -20605,11 +20618,11 @@
       </c>
       <c r="AD40" s="63">
         <f>'[5]Project Summary'!$J$11</f>
-        <v>1.4584164761904759</v>
+        <v>1.6253984761904758</v>
       </c>
       <c r="AE40" s="88">
         <f t="shared" si="9"/>
-        <v>0.87330327915597361</v>
+        <v>0.97329250071285978</v>
       </c>
       <c r="AF40" s="146">
         <f>'[5]Project Summary'!$L$11</f>
@@ -20851,11 +20864,11 @@
       </c>
       <c r="R43" s="125">
         <f>SUM(R36:R42)</f>
-        <v>2.3747605714285718</v>
+        <v>2.4223796190476197</v>
       </c>
       <c r="S43" s="126">
         <f>R43/Q43</f>
-        <v>2.6157734943863935</v>
+        <v>2.6682253685199186</v>
       </c>
       <c r="T43" s="127">
         <f>SUM(T36:T42)</f>
@@ -20867,11 +20880,11 @@
       </c>
       <c r="V43" s="125">
         <f>SUM(V36:V42)</f>
-        <v>1.3182723809523809</v>
+        <v>1.7007692380952382</v>
       </c>
       <c r="W43" s="126">
         <f>V43/U43</f>
-        <v>1.0219165743816905</v>
+        <v>1.3184257659653009</v>
       </c>
       <c r="X43" s="147">
         <f>SUM(X36:X42)</f>
@@ -20899,11 +20912,11 @@
       </c>
       <c r="AD43" s="125">
         <f>SUM(AD36:AD42)</f>
-        <v>3.4306124523809518</v>
+        <v>3.5975944523809518</v>
       </c>
       <c r="AE43" s="126">
         <f>AD43/AC43</f>
-        <v>0.36226108261678475</v>
+        <v>0.37989381756926627</v>
       </c>
       <c r="AF43" s="147">
         <f>SUM(AF36:AF42)</f>
@@ -20965,7 +20978,7 @@
       </c>
       <c r="R45" s="112">
         <f>N27-R43</f>
-        <v>14.765296414285716</v>
+        <v>14.932278414285717</v>
       </c>
       <c r="S45" s="113"/>
       <c r="T45" s="112"/>
@@ -21178,7 +21191,7 @@
       </c>
       <c r="AA54" s="169">
         <f>'[5]Project Summary'!$L$19</f>
-        <v>0.1708152380952381</v>
+        <v>0.12319619047619046</v>
       </c>
       <c r="AB54" s="169"/>
       <c r="AC54" s="169">
@@ -21187,7 +21200,7 @@
       </c>
       <c r="AD54" s="169">
         <f>SUM(W54:AC54)</f>
-        <v>0.78298600952380948</v>
+        <v>0.73536696190476181</v>
       </c>
     </row>
     <row r="55" spans="12:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -21384,7 +21397,7 @@
       </c>
       <c r="AA58" s="167">
         <f t="shared" si="11"/>
-        <v>1.8097857238095236</v>
+        <v>1.762166676190476</v>
       </c>
       <c r="AB58" s="167">
         <f t="shared" si="11"/>
@@ -21396,7 +21409,7 @@
       </c>
       <c r="AD58" s="167">
         <f t="shared" si="11"/>
-        <v>10.052724276190478</v>
+        <v>10.005105228571431</v>
       </c>
     </row>
     <row r="59" spans="12:30" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -21453,13 +21466,6 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="16">
-    <mergeCell ref="S18:V18"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="AG34:AJ34"/>
-    <mergeCell ref="AC34:AF34"/>
-    <mergeCell ref="Y34:AB34"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="Q34:T34"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="L52:Q52"/>
@@ -21469,6 +21475,13 @@
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="G7:I7"/>
+    <mergeCell ref="S18:V18"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="AG34:AJ34"/>
+    <mergeCell ref="AC34:AF34"/>
+    <mergeCell ref="Y34:AB34"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="Q34:T34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -21521,20 +21534,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:36" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="254" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="254"/>
-      <c r="D1" s="254"/>
-      <c r="E1" s="254"/>
-      <c r="F1" s="254"/>
+      <c r="B1" s="257" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="257"/>
+      <c r="D1" s="257"/>
+      <c r="E1" s="257"/>
+      <c r="F1" s="257"/>
       <c r="H1" s="37" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="35"/>
       <c r="J1" s="36">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="Q1" s="235" t="s">
         <v>77</v>
@@ -21544,19 +21557,19 @@
       <c r="T1" s="235"/>
     </row>
     <row r="2" spans="2:36" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="255" t="s">
+      <c r="B2" s="258" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="255"/>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="255" t="s">
+      <c r="H2" s="258" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
@@ -21576,12 +21589,12 @@
         <f>$S$9</f>
         <v>0</v>
       </c>
-      <c r="H3" s="256" t="str">
+      <c r="H3" s="259" t="str">
         <f>CONCATENATE($Z$9, " / ", $Y$9)</f>
         <v>9 / 17</v>
       </c>
-      <c r="I3" s="257"/>
-      <c r="J3" s="258"/>
+      <c r="I3" s="260"/>
+      <c r="J3" s="261"/>
       <c r="L3" s="5">
         <v>8</v>
       </c>
@@ -21722,12 +21735,12 @@
         <f>$W$19</f>
         <v>6.6640613999999996</v>
       </c>
-      <c r="H6" s="259" t="str">
+      <c r="H6" s="254" t="str">
         <f>CONCATENATE($U$9," / ",AA9)</f>
         <v>17 / 20</v>
       </c>
-      <c r="I6" s="260"/>
-      <c r="J6" s="261"/>
+      <c r="I6" s="255"/>
+      <c r="J6" s="256"/>
       <c r="L6" s="10"/>
       <c r="Q6" s="11" t="s">
         <v>86</v>
@@ -22496,17 +22509,17 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="11">
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="V12:AA12"/>
-    <mergeCell ref="Q23:T23"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="V12:AA12"/>
+    <mergeCell ref="Q23:T23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -22565,13 +22578,10 @@
       </c>
       <c r="I1" s="98">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="K1" s="170"/>
-      <c r="L1" s="97">
-        <f>14.76+2.92+1.32</f>
-        <v>19</v>
-      </c>
+      <c r="L1" s="97"/>
       <c r="M1" s="110"/>
       <c r="N1" s="110"/>
       <c r="O1" s="110"/>
@@ -22602,21 +22612,21 @@
     <row r="3" spans="2:32" ht="134.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="239" t="str">
         <f>CONCATENATE("₹ ",ROUND($N$27,2)," / ",ROUND($M$27,2)," (",ROUND($O$27,3)*100,"%)")</f>
-        <v>₹ 15.1 / 36.05 (41.9%)</v>
+        <v>₹ 15.45 / 36.05 (42.9%)</v>
       </c>
       <c r="C3" s="240"/>
       <c r="D3" s="241"/>
       <c r="F3" s="161" t="str">
         <f>CONCATENATE("₹ ", ROUND($U$21,2), "  /  ", "₹ ", ROUND($T$21,2))</f>
-        <v>₹ 2.92  /  ₹ 1.52</v>
+        <v>₹ 3.14  /  ₹ 1.52</v>
       </c>
       <c r="G3" s="160" t="str">
         <f>CONCATENATE("₹ ", ROUND($U$22,2), "  /  ", "₹ ", ROUND($T$22,2))</f>
-        <v>₹ 1.32  /  ₹ 1.87</v>
+        <v>₹ 1.7  /  ₹ 1.87</v>
       </c>
       <c r="I3" s="85" t="str">
         <f ca="1">CONCATENATE("₹ ",ROUND($N$11,2), "  |  ", "₹ ",ROUND($O$11,2))</f>
-        <v>₹ 0.34  |  ₹ 19.32</v>
+        <v>₹ 0  |  ₹ 20.1</v>
       </c>
       <c r="L3" s="114" t="s">
         <v>5</v>
@@ -22707,11 +22717,11 @@
       </c>
       <c r="T4" s="69">
         <f>'[1]Project Summary'!$D$21</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U4" s="69">
         <f ca="1">'[1]Project Summary'!$F$21</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V4" s="69">
         <f>'[1]Project Summary'!$Q$3</f>
@@ -22739,7 +22749,7 @@
         <v>105</v>
       </c>
       <c r="N5" s="102">
-        <f ca="1">'[2]Project Summary'!$D$7</f>
+        <f>'[2]Project Summary'!$D$7</f>
         <v>0</v>
       </c>
       <c r="O5" s="102">
@@ -22767,7 +22777,7 @@
         <v>1</v>
       </c>
       <c r="U5" s="69">
-        <f ca="1">'[2]Project Summary'!$F$20</f>
+        <f>'[2]Project Summary'!$F$20</f>
         <v>1</v>
       </c>
       <c r="V5" s="69">
@@ -22790,19 +22800,19 @@
       <c r="C6" s="8"/>
       <c r="D6" s="84">
         <f>$S$11-AC54-AC55</f>
-        <v>9.7016765666666664</v>
+        <v>9.5204860666666669</v>
       </c>
       <c r="F6" s="154" t="str">
         <f ca="1">CONCATENATE($U$11, "      |    ", $T$11)</f>
-        <v>30      |    48</v>
+        <v>29      |    48</v>
       </c>
       <c r="G6" s="156" t="str">
         <f>CONCATENATE($P$11," / ",V11)</f>
-        <v>20 / 26</v>
+        <v>21 / 26</v>
       </c>
       <c r="I6" s="84">
         <f>$S$11</f>
-        <v>10.853153976190475</v>
+        <v>10.449389428571429</v>
       </c>
       <c r="L6" s="109" t="s">
         <v>116</v>
@@ -22812,12 +22822,12 @@
         <v>87</v>
       </c>
       <c r="N6" s="102">
-        <f ca="1">'[3]Project Summary'!$D$7</f>
-        <v>4.09524E-2</v>
+        <f>'[3]Project Summary'!$D$7</f>
+        <v>0</v>
       </c>
       <c r="O6" s="102">
         <f>'[3]Project Summary'!$E$7</f>
-        <v>3.0213570380952395</v>
+        <v>3.1236478952380966</v>
       </c>
       <c r="P6" s="105">
         <f>'[3]Project Summary'!$F$7</f>
@@ -22829,7 +22839,7 @@
       </c>
       <c r="R6" s="82">
         <f>'[3]Project Summary'!$D$13</f>
-        <v>54.517780838095234</v>
+        <v>54.620071695238089</v>
       </c>
       <c r="S6" s="82">
         <f>'[3]Project Summary'!$E$13</f>
@@ -22840,7 +22850,7 @@
         <v>23</v>
       </c>
       <c r="U6" s="69">
-        <f ca="1">'[3]Project Summary'!$F$20</f>
+        <f>'[3]Project Summary'!$F$20</f>
         <v>11</v>
       </c>
       <c r="V6" s="69">
@@ -22882,7 +22892,7 @@
       </c>
       <c r="N7" s="102">
         <f ca="1">'[4]Project Summary'!$D$7</f>
-        <v>0.20576959523809524</v>
+        <v>0</v>
       </c>
       <c r="O7" s="102">
         <f>'[4]Project Summary'!$E$7</f>
@@ -22932,19 +22942,19 @@
       </c>
       <c r="M8" s="69">
         <f>'[5]Project Summary'!$B$7</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N8" s="102">
         <f ca="1">'[5]Project Summary'!$D$7</f>
-        <v>9.5238095238095247E-6</v>
+        <v>0</v>
       </c>
       <c r="O8" s="102">
         <f>'[5]Project Summary'!$E$7</f>
-        <v>5.2190769142857167</v>
+        <v>5.5354573904761928</v>
       </c>
       <c r="P8" s="105">
         <f>'[5]Project Summary'!$F$7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="82">
         <f>'[5]Project Summary'!$C$13</f>
@@ -22952,15 +22962,15 @@
       </c>
       <c r="R8" s="82">
         <f>'[5]Project Summary'!$D$13</f>
-        <v>37.055928895238097</v>
+        <v>37.550735942857152</v>
       </c>
       <c r="S8" s="82">
         <f>'[5]Project Summary'!$E$13</f>
-        <v>1.8097857238095234</v>
+        <v>1.7621666761904762</v>
       </c>
       <c r="T8" s="69">
         <f>'[5]Project Summary'!$D$20</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8" s="69">
         <f ca="1">'[5]Project Summary'!$F$20</f>
@@ -22988,12 +22998,12 @@
         <v>18</v>
       </c>
       <c r="N9" s="102">
-        <f>'[6]Project Summary'!$D$7</f>
-        <v>1.6549600000000001E-2</v>
+        <f ca="1">'[6]Project Summary'!$D$7</f>
+        <v>0</v>
       </c>
       <c r="O9" s="103">
         <f>'[6]Project Summary'!$E$7</f>
-        <v>0.87958619999999998</v>
+        <v>1.2357317000000001</v>
       </c>
       <c r="P9" s="106">
         <f>'[6]Project Summary'!$F$7</f>
@@ -23005,18 +23015,18 @@
       </c>
       <c r="R9" s="82">
         <f>'[6]Project Summary'!$D$13</f>
-        <v>4.0424424999999999</v>
+        <v>4.3985880000000002</v>
       </c>
       <c r="S9" s="82">
         <f>'[6]Project Summary'!$E$13</f>
-        <v>1.0304297</v>
+        <v>0.6742842</v>
       </c>
       <c r="T9" s="69">
         <f>'[6]Project Summary'!$D$20</f>
         <v>7</v>
       </c>
       <c r="U9" s="69">
-        <f>'[6]Project Summary'!$F$20</f>
+        <f ca="1">'[6]Project Summary'!$F$20</f>
         <v>7</v>
       </c>
       <c r="V9" s="69">
@@ -23041,7 +23051,7 @@
       </c>
       <c r="N10" s="102">
         <f ca="1">'[7]Project Summary'!$D$7</f>
-        <v>7.3509714285714289E-2</v>
+        <v>0</v>
       </c>
       <c r="O10" s="103">
         <f>'[7]Project Summary'!$E$7</f>
@@ -23089,19 +23099,19 @@
       </c>
       <c r="M11" s="117">
         <f t="shared" ref="M11:W11" si="0">SUM(M4:M10)</f>
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N11" s="118">
         <f t="shared" ca="1" si="0"/>
-        <v>0.33679083333333337</v>
+        <v>0</v>
       </c>
       <c r="O11" s="118">
         <f t="shared" si="0"/>
-        <v>19.323639376190481</v>
+        <v>20.098456209523814</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q11" s="120">
         <f t="shared" si="0"/>
@@ -23109,11 +23119,11 @@
       </c>
       <c r="R11" s="120">
         <f t="shared" si="0"/>
-        <v>475.35149895714284</v>
+        <v>476.3047423619048</v>
       </c>
       <c r="S11" s="120">
         <f t="shared" si="0"/>
-        <v>10.853153976190475</v>
+        <v>10.449389428571429</v>
       </c>
       <c r="T11" s="121">
         <f t="shared" si="0"/>
@@ -23121,7 +23131,7 @@
       </c>
       <c r="U11" s="121">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V11" s="121">
         <f t="shared" si="0"/>
@@ -23254,11 +23264,11 @@
       </c>
       <c r="U20" s="64">
         <f>N43</f>
-        <v>4.6723711904761913</v>
+        <v>4.8369220904761914</v>
       </c>
       <c r="V20" s="88">
         <f>O43</f>
-        <v>0.40545908592659802</v>
+        <v>0.41973848599618013</v>
       </c>
       <c r="W20" s="64">
         <f>P43</f>
@@ -23307,11 +23317,11 @@
       </c>
       <c r="U21" s="64">
         <f>R43</f>
-        <v>2.9198205714285717</v>
+        <v>3.1423946190476197</v>
       </c>
       <c r="V21" s="88">
         <f>S43</f>
-        <v>1.92629195924809</v>
+        <v>2.0731306391523501</v>
       </c>
       <c r="W21" s="64">
         <f>T43</f>
@@ -23360,11 +23370,11 @@
       </c>
       <c r="U22" s="64">
         <f>V43</f>
-        <v>1.3182723809523809</v>
+        <v>1.7007692380952382</v>
       </c>
       <c r="V22" s="88">
         <f>W43</f>
-        <v>0.70495849248790421</v>
+        <v>0.90950226636108999</v>
       </c>
       <c r="W22" s="64">
         <f>X43</f>
@@ -23442,11 +23452,11 @@
       </c>
       <c r="N24" s="18">
         <f>'[5]Project Summary'!$J$13-R40</f>
-        <v>4.1363054857142858</v>
+        <v>4.3032874857142858</v>
       </c>
       <c r="O24" s="19">
         <f t="shared" si="1"/>
-        <v>0.68704711943287278</v>
+        <v>0.7147831032699874</v>
       </c>
       <c r="P24" s="18">
         <f>'[5]Project Summary'!$L$13-T40</f>
@@ -23454,7 +23464,7 @@
       </c>
       <c r="Q24" s="18">
         <f t="shared" si="2"/>
-        <v>1.0799188142857146</v>
+        <v>0.9129368142857146</v>
       </c>
       <c r="R24" s="228">
         <f t="shared" si="3"/>
@@ -23472,11 +23482,11 @@
       </c>
       <c r="U24" s="64">
         <f>AD43</f>
-        <v>3.7617804523809517</v>
+        <v>3.9454020523809517</v>
       </c>
       <c r="V24" s="88">
         <f>AE43</f>
-        <v>0.36101539850105097</v>
+        <v>0.37863743304999531</v>
       </c>
       <c r="W24" s="64">
         <f>AF43</f>
@@ -23498,11 +23508,11 @@
       </c>
       <c r="N25" s="18">
         <f>'[6]Project Summary'!$J$13-R41</f>
-        <v>0.3345262</v>
+        <v>0.51571670000000014</v>
       </c>
       <c r="O25" s="19">
         <f t="shared" si="1"/>
-        <v>0.17813758930078144</v>
+        <v>0.27462282386298692</v>
       </c>
       <c r="P25" s="18">
         <f>'[6]Project Summary'!$L$13-T41</f>
@@ -23510,7 +23520,7 @@
       </c>
       <c r="Q25" s="18">
         <f t="shared" si="2"/>
-        <v>1.2854737999999999</v>
+        <v>1.1042832999999996</v>
       </c>
       <c r="R25" s="228">
         <f t="shared" si="3"/>
@@ -23581,11 +23591,11 @@
       </c>
       <c r="N27" s="18">
         <f>SUM(N20:N26)</f>
-        <v>15.099822614285713</v>
+        <v>15.447995114285714</v>
       </c>
       <c r="O27" s="19">
         <f>N27/M27</f>
-        <v>0.41884816163262256</v>
+        <v>0.42850598446148586</v>
       </c>
       <c r="P27" s="18">
         <f>SUM(P20:P26)</f>
@@ -23593,7 +23603,7 @@
       </c>
       <c r="Q27" s="18">
         <f t="shared" si="2"/>
-        <v>12.80667238571429</v>
+        <v>12.458499885714289</v>
       </c>
       <c r="R27" s="228">
         <f>M27-P27</f>
@@ -23673,7 +23683,7 @@
       <c r="AB34" s="237"/>
       <c r="AC34" s="232" t="str">
         <f ca="1">CONCATENATE("Expected Registrations in August ",$D$3,"'",$I$3," ")</f>
-        <v xml:space="preserve">Expected Registrations in August '₹ 0.34  |  ₹ 19.32 </v>
+        <v xml:space="preserve">Expected Registrations in August '₹ 0  |  ₹ 20.1 </v>
       </c>
       <c r="AD34" s="233"/>
       <c r="AE34" s="233"/>
@@ -24038,11 +24048,11 @@
       </c>
       <c r="V38" s="63">
         <f>'[3]Project Summary'!$J$9</f>
-        <v>0.87295247619047611</v>
+        <v>0.97524333333333335</v>
       </c>
       <c r="W38" s="88">
         <f t="shared" si="9"/>
-        <v>1.2470749659863944</v>
+        <v>1.3932047619047621</v>
       </c>
       <c r="X38" s="146">
         <f>'[3]Project Summary'!$L$9</f>
@@ -24240,11 +24250,11 @@
       </c>
       <c r="R40" s="63">
         <f>'[5]Project Summary'!$J$8</f>
-        <v>1.001371904761905</v>
+        <v>1.0489909523809526</v>
       </c>
       <c r="S40" s="88">
         <f t="shared" si="8"/>
-        <v>2.4963333103866607</v>
+        <v>2.6150434661390149</v>
       </c>
       <c r="T40" s="124">
         <f>'[5]Project Summary'!$L$8</f>
@@ -24256,11 +24266,11 @@
       </c>
       <c r="V40" s="63">
         <f>'[5]Project Summary'!$J$9</f>
-        <v>8.6151904761904763E-2</v>
+        <v>0.36635790476190477</v>
       </c>
       <c r="W40" s="88">
         <f t="shared" si="9"/>
-        <v>0.95724338624338634</v>
+        <v>4.0706433862433862</v>
       </c>
       <c r="X40" s="146">
         <f>'[5]Project Summary'!$L$9</f>
@@ -24288,11 +24298,11 @@
       </c>
       <c r="AD40" s="63">
         <f>'[5]Project Summary'!$J$11</f>
-        <v>1.4584164761904759</v>
+        <v>1.6253984761904758</v>
       </c>
       <c r="AE40" s="88">
         <f t="shared" si="11"/>
-        <v>0.87330327915597361</v>
+        <v>0.97329250071285978</v>
       </c>
       <c r="AF40" s="146">
         <f>'[5]Project Summary'!$L$11</f>
@@ -24333,11 +24343,11 @@
       </c>
       <c r="N41" s="63">
         <f>'[6]Project Summary'!$J$7</f>
-        <v>3.3582E-3</v>
+        <v>0.16790910000000001</v>
       </c>
       <c r="O41" s="88">
         <f t="shared" si="7"/>
-        <v>2.0000107200860463E-2</v>
+        <v>1</v>
       </c>
       <c r="P41" s="146">
         <f>'[6]Project Summary'!$L$7</f>
@@ -24349,11 +24359,11 @@
       </c>
       <c r="R41" s="63">
         <f>'[6]Project Summary'!$J$8</f>
-        <v>0.54505999999999999</v>
+        <v>0.72001499999999996</v>
       </c>
       <c r="S41" s="88">
         <f t="shared" si="8"/>
-        <v>0.89661165805712639</v>
+        <v>1.1844087677980439</v>
       </c>
       <c r="T41" s="124">
         <f>'[6]Project Summary'!$L$8</f>
@@ -24397,11 +24407,11 @@
       </c>
       <c r="AD41" s="63">
         <f>'[6]Project Summary'!$J$11</f>
-        <v>0.33116800000000002</v>
+        <v>0.34780759999999999</v>
       </c>
       <c r="AE41" s="88">
         <f t="shared" si="11"/>
-        <v>0.34859789473684216</v>
+        <v>0.36611326315789477</v>
       </c>
       <c r="AF41" s="146">
         <f>'[6]Project Summary'!$L$11</f>
@@ -24553,11 +24563,11 @@
       </c>
       <c r="N43" s="192">
         <f>SUM(N36:N42)</f>
-        <v>4.6723711904761913</v>
+        <v>4.8369220904761914</v>
       </c>
       <c r="O43" s="193">
         <f t="shared" si="7"/>
-        <v>0.40545908592659802</v>
+        <v>0.41973848599618013</v>
       </c>
       <c r="P43" s="194">
         <f>SUM(P36:P42)</f>
@@ -24569,11 +24579,11 @@
       </c>
       <c r="R43" s="192">
         <f>SUM(R36:R42)</f>
-        <v>2.9198205714285717</v>
+        <v>3.1423946190476197</v>
       </c>
       <c r="S43" s="193">
         <f t="shared" si="8"/>
-        <v>1.92629195924809</v>
+        <v>2.0731306391523501</v>
       </c>
       <c r="T43" s="195">
         <f>SUM(T36:T42)</f>
@@ -24585,11 +24595,11 @@
       </c>
       <c r="V43" s="192">
         <f>SUM(V36:V42)</f>
-        <v>1.3182723809523809</v>
+        <v>1.7007692380952382</v>
       </c>
       <c r="W43" s="193">
         <f t="shared" si="9"/>
-        <v>0.70495849248790421</v>
+        <v>0.90950226636108999</v>
       </c>
       <c r="X43" s="194">
         <f>SUM(X36:X42)</f>
@@ -24617,11 +24627,11 @@
       </c>
       <c r="AD43" s="192">
         <f>SUM(AD36:AD42)</f>
-        <v>3.7617804523809517</v>
+        <v>3.9454020523809517</v>
       </c>
       <c r="AE43" s="193">
         <f t="shared" si="11"/>
-        <v>0.36101539850105097</v>
+        <v>0.37863743304999531</v>
       </c>
       <c r="AF43" s="194">
         <f>SUM(AF36:AF42)</f>
@@ -24686,7 +24696,7 @@
       </c>
       <c r="R45" s="112">
         <f>N27-R43</f>
-        <v>12.180002042857142</v>
+        <v>12.305600495238094</v>
       </c>
       <c r="S45" s="158"/>
       <c r="T45" s="112"/>
@@ -24857,7 +24867,7 @@
       </c>
       <c r="AA53" s="169">
         <f>'[6]Project Summary'!$L$18</f>
-        <v>0.32914549999999998</v>
+        <v>0.16459460000000001</v>
       </c>
       <c r="AB53" s="169">
         <f>'[7]Project Summary'!$L$18</f>
@@ -24865,7 +24875,7 @@
       </c>
       <c r="AC53" s="169">
         <f>SUM(V53:AB53)</f>
-        <v>7.1582927523809534</v>
+        <v>6.9937418523809534</v>
       </c>
     </row>
     <row r="54" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -24909,11 +24919,11 @@
       </c>
       <c r="Z54" s="169">
         <f>'[5]Project Summary'!$L$19</f>
-        <v>0.1708152380952381</v>
+        <v>0.12319619047619046</v>
       </c>
       <c r="AA54" s="169">
         <f>'[6]Project Summary'!$L$19</f>
-        <v>0.36849140000000002</v>
+        <v>0.1935364</v>
       </c>
       <c r="AB54" s="169">
         <f>'[7]Project Summary'!$L$19</f>
@@ -24921,7 +24931,7 @@
       </c>
       <c r="AC54" s="169">
         <f>SUM(V54:AB54)</f>
-        <v>1.1514774095238094</v>
+        <v>0.92890336190476175</v>
       </c>
     </row>
     <row r="55" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -25087,7 +25097,7 @@
       </c>
       <c r="AA57" s="169">
         <f>'[6]Project Summary'!$L$22</f>
-        <v>0.3327928</v>
+        <v>0.31615320000000002</v>
       </c>
       <c r="AB57" s="169">
         <f>'[7]Project Summary'!$L$22</f>
@@ -25095,7 +25105,7 @@
       </c>
       <c r="AC57" s="169">
         <f>SUM(V57:AB57)</f>
-        <v>2.1324550476190476</v>
+        <v>2.1158154476190476</v>
       </c>
     </row>
     <row r="58" spans="12:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -25139,11 +25149,11 @@
       </c>
       <c r="Z58" s="167">
         <f t="shared" si="14"/>
-        <v>1.8097857238095236</v>
+        <v>1.762166676190476</v>
       </c>
       <c r="AA58" s="167">
         <f t="shared" si="14"/>
-        <v>1.0304297</v>
+        <v>0.6742842</v>
       </c>
       <c r="AB58" s="167">
         <f t="shared" si="14"/>
@@ -25151,7 +25161,7 @@
       </c>
       <c r="AC58" s="167">
         <f t="shared" si="14"/>
-        <v>10.853153976190477</v>
+        <v>10.449389428571429</v>
       </c>
     </row>
     <row r="59" spans="12:29" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -25524,11 +25534,11 @@
       </c>
       <c r="P2" s="219">
         <f>Overall_Draft!T4</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="219">
         <f ca="1">Overall_Draft!U4</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" s="219">
         <f>Overall_Draft!V4</f>
@@ -25701,7 +25711,7 @@
         <v>105</v>
       </c>
       <c r="J3" s="209">
-        <f ca="1">Overall_Draft!N5</f>
+        <f>Overall_Draft!N5</f>
         <v>0</v>
       </c>
       <c r="K3" s="209">
@@ -25729,7 +25739,7 @@
         <v>1</v>
       </c>
       <c r="Q3" s="123">
-        <f ca="1">Overall_Draft!U5</f>
+        <f>Overall_Draft!U5</f>
         <v>1</v>
       </c>
       <c r="R3" s="123">
@@ -25853,11 +25863,11 @@
       </c>
       <c r="AX3" s="209">
         <f>Overall!U21</f>
-        <v>2.3747605714285718</v>
+        <v>2.4223796190476197</v>
       </c>
       <c r="AY3" s="210">
         <f>Overall!V21</f>
-        <v>2.6157734943863935</v>
+        <v>2.6682253685199186</v>
       </c>
       <c r="AZ3" s="209">
         <f>Overall!W21</f>
@@ -25903,12 +25913,12 @@
         <v>87</v>
       </c>
       <c r="J4" s="209">
-        <f ca="1">Overall_Draft!N6</f>
-        <v>4.09524E-2</v>
+        <f>Overall_Draft!N6</f>
+        <v>0</v>
       </c>
       <c r="K4" s="209">
         <f>Overall_Draft!O6</f>
-        <v>3.0213570380952395</v>
+        <v>3.1236478952380966</v>
       </c>
       <c r="L4" s="123">
         <f>Overall_Draft!P6</f>
@@ -25920,7 +25930,7 @@
       </c>
       <c r="N4" s="209">
         <f>Overall_Draft!R6</f>
-        <v>54.517780838095234</v>
+        <v>54.620071695238089</v>
       </c>
       <c r="O4" s="209">
         <f>Overall_Draft!S6</f>
@@ -25931,7 +25941,7 @@
         <v>23</v>
       </c>
       <c r="Q4" s="123">
-        <f ca="1">Overall_Draft!U6</f>
+        <f>Overall_Draft!U6</f>
         <v>11</v>
       </c>
       <c r="R4" s="123">
@@ -25986,11 +25996,11 @@
       </c>
       <c r="AE4" s="209">
         <f>Overall_Draft!V38</f>
-        <v>0.87295247619047611</v>
+        <v>0.97524333333333335</v>
       </c>
       <c r="AF4" s="210">
         <f>Overall_Draft!W38</f>
-        <v>1.2470749659863944</v>
+        <v>1.3932047619047621</v>
       </c>
       <c r="AG4" s="209">
         <f>Overall_Draft!X38</f>
@@ -26055,11 +26065,11 @@
       </c>
       <c r="AX4" s="209">
         <f>Overall!U22</f>
-        <v>1.3182723809523809</v>
+        <v>1.7007692380952382</v>
       </c>
       <c r="AY4" s="210">
         <f>Overall!V22</f>
-        <v>1.0219165743816905</v>
+        <v>1.3184257659653009</v>
       </c>
       <c r="AZ4" s="209">
         <f>Overall!W22</f>
@@ -26106,7 +26116,7 @@
       </c>
       <c r="J5" s="209">
         <f ca="1">Overall_Draft!N7</f>
-        <v>0.20576959523809524</v>
+        <v>0</v>
       </c>
       <c r="K5" s="209">
         <f>Overall_Draft!O7</f>
@@ -26284,11 +26294,11 @@
       </c>
       <c r="D6" s="221">
         <f>Overall_Draft!N24</f>
-        <v>4.1363054857142858</v>
+        <v>4.3032874857142858</v>
       </c>
       <c r="E6" s="222">
         <f t="shared" si="0"/>
-        <v>0.68704711943287278</v>
+        <v>0.7147831032699874</v>
       </c>
       <c r="F6" s="221">
         <f>Overall_Draft!P24</f>
@@ -26296,7 +26306,7 @@
       </c>
       <c r="G6" s="221">
         <f>Overall_Draft!Q24</f>
-        <v>1.0799188142857146</v>
+        <v>0.9129368142857146</v>
       </c>
       <c r="H6" s="123" t="str">
         <f>Overall_Draft!L8</f>
@@ -26304,19 +26314,19 @@
       </c>
       <c r="I6" s="123">
         <f>Overall_Draft!M8</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J6" s="209">
         <f ca="1">Overall_Draft!N8</f>
-        <v>9.5238095238095247E-6</v>
+        <v>0</v>
       </c>
       <c r="K6" s="209">
         <f>Overall_Draft!O8</f>
-        <v>5.2190769142857167</v>
+        <v>5.5354573904761928</v>
       </c>
       <c r="L6" s="123">
         <f>Overall_Draft!P8</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" s="209">
         <f>Overall_Draft!Q8</f>
@@ -26324,15 +26334,15 @@
       </c>
       <c r="N6" s="209">
         <f>Overall_Draft!R8</f>
-        <v>37.055928895238097</v>
+        <v>37.550735942857152</v>
       </c>
       <c r="O6" s="209">
         <f>Overall_Draft!S8</f>
-        <v>1.8097857238095234</v>
+        <v>1.7621666761904762</v>
       </c>
       <c r="P6" s="123">
         <f>Overall_Draft!T8</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q6" s="123">
         <f ca="1">Overall_Draft!U8</f>
@@ -26374,11 +26384,11 @@
       </c>
       <c r="AA6" s="209">
         <f>Overall_Draft!R40</f>
-        <v>1.001371904761905</v>
+        <v>1.0489909523809526</v>
       </c>
       <c r="AB6" s="210">
         <f>Overall_Draft!S40</f>
-        <v>2.4963333103866607</v>
+        <v>2.6150434661390149</v>
       </c>
       <c r="AC6" s="209">
         <f>Overall_Draft!T40</f>
@@ -26390,11 +26400,11 @@
       </c>
       <c r="AE6" s="209">
         <f>Overall_Draft!V40</f>
-        <v>8.6151904761904763E-2</v>
+        <v>0.36635790476190477</v>
       </c>
       <c r="AF6" s="210">
         <f>Overall_Draft!W40</f>
-        <v>0.95724338624338634</v>
+        <v>4.0706433862433862</v>
       </c>
       <c r="AG6" s="209">
         <f>Overall_Draft!X40</f>
@@ -26422,11 +26432,11 @@
       </c>
       <c r="AM6" s="209">
         <f>Overall_Draft!AD40</f>
-        <v>1.4584164761904759</v>
+        <v>1.6253984761904758</v>
       </c>
       <c r="AN6" s="210">
         <f>Overall_Draft!AE40</f>
-        <v>0.87330327915597361</v>
+        <v>0.97329250071285978</v>
       </c>
       <c r="AO6" s="209">
         <f>Overall_Draft!AF40</f>
@@ -26459,11 +26469,11 @@
       </c>
       <c r="AX6" s="209">
         <f>Overall!U24</f>
-        <v>3.4306124523809518</v>
+        <v>3.5975944523809518</v>
       </c>
       <c r="AY6" s="210">
         <f>Overall!V24</f>
-        <v>0.36226108261678475</v>
+        <v>0.37989381756926627</v>
       </c>
       <c r="AZ6" s="209">
         <f>Overall!W24</f>
@@ -26486,11 +26496,11 @@
       </c>
       <c r="D7" s="221">
         <f>Overall_Draft!N25</f>
-        <v>0.3345262</v>
+        <v>0.51571670000000014</v>
       </c>
       <c r="E7" s="222">
         <f t="shared" si="0"/>
-        <v>0.17813758930078144</v>
+        <v>0.27462282386298692</v>
       </c>
       <c r="F7" s="221">
         <f>Overall_Draft!P25</f>
@@ -26498,7 +26508,7 @@
       </c>
       <c r="G7" s="221">
         <f>Overall_Draft!Q25</f>
-        <v>1.2854737999999999</v>
+        <v>1.1042832999999996</v>
       </c>
       <c r="H7" s="123" t="str">
         <f>Overall_Draft!L9</f>
@@ -26509,12 +26519,12 @@
         <v>18</v>
       </c>
       <c r="J7" s="209">
-        <f>Overall_Draft!N9</f>
-        <v>1.6549600000000001E-2</v>
+        <f ca="1">Overall_Draft!N9</f>
+        <v>0</v>
       </c>
       <c r="K7" s="209">
         <f>Overall_Draft!O9</f>
-        <v>0.87958619999999998</v>
+        <v>1.2357317000000001</v>
       </c>
       <c r="L7" s="123">
         <f>Overall_Draft!P9</f>
@@ -26526,18 +26536,18 @@
       </c>
       <c r="N7" s="209">
         <f>Overall_Draft!R9</f>
-        <v>4.0424424999999999</v>
+        <v>4.3985880000000002</v>
       </c>
       <c r="O7" s="209">
         <f>Overall_Draft!S9</f>
-        <v>1.0304297</v>
+        <v>0.6742842</v>
       </c>
       <c r="P7" s="123">
         <f>Overall_Draft!T9</f>
         <v>7</v>
       </c>
       <c r="Q7" s="123">
-        <f>Overall_Draft!U9</f>
+        <f ca="1">Overall_Draft!U9</f>
         <v>7</v>
       </c>
       <c r="R7" s="123">
@@ -26560,11 +26570,11 @@
       </c>
       <c r="W7" s="209">
         <f>Overall_Draft!N41</f>
-        <v>3.3582E-3</v>
+        <v>0.16790910000000001</v>
       </c>
       <c r="X7" s="210">
         <f>Overall_Draft!O41</f>
-        <v>2.0000107200860463E-2</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="209">
         <f>Overall_Draft!P41</f>
@@ -26576,11 +26586,11 @@
       </c>
       <c r="AA7" s="209">
         <f>Overall_Draft!R41</f>
-        <v>0.54505999999999999</v>
+        <v>0.72001499999999996</v>
       </c>
       <c r="AB7" s="210">
         <f>Overall_Draft!S41</f>
-        <v>0.89661165805712639</v>
+        <v>1.1844087677980439</v>
       </c>
       <c r="AC7" s="209">
         <f>Overall_Draft!T41</f>
@@ -26624,11 +26634,11 @@
       </c>
       <c r="AM7" s="209">
         <f>Overall_Draft!AD41</f>
-        <v>0.33116800000000002</v>
+        <v>0.34780759999999999</v>
       </c>
       <c r="AN7" s="210">
         <f>Overall_Draft!AE41</f>
-        <v>0.34859789473684216</v>
+        <v>0.36611326315789477</v>
       </c>
       <c r="AO7" s="209">
         <f>Overall_Draft!AF41</f>
@@ -26712,7 +26722,7 @@
       </c>
       <c r="J8" s="209">
         <f ca="1">Overall_Draft!N10</f>
-        <v>7.3509714285714289E-2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="209">
         <f>Overall_Draft!O10</f>
@@ -26864,11 +26874,11 @@
       </c>
       <c r="D9" s="224">
         <f>Overall_Draft!N27</f>
-        <v>15.099822614285713</v>
+        <v>15.447995114285714</v>
       </c>
       <c r="E9" s="225">
         <f t="shared" si="0"/>
-        <v>0.41884816163262256</v>
+        <v>0.42850598446148586</v>
       </c>
       <c r="F9" s="224">
         <f>Overall_Draft!P27</f>
@@ -26876,7 +26886,7 @@
       </c>
       <c r="G9" s="224">
         <f>Overall_Draft!Q27</f>
-        <v>12.80667238571429</v>
+        <v>12.458499885714289</v>
       </c>
       <c r="H9" s="226" t="str">
         <f>Overall_Draft!L11</f>
@@ -26884,19 +26894,19 @@
       </c>
       <c r="I9" s="226">
         <f>Overall_Draft!M11</f>
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J9" s="213">
         <f ca="1">Overall_Draft!N11</f>
-        <v>0.33679083333333337</v>
+        <v>0</v>
       </c>
       <c r="K9" s="213">
         <f>Overall_Draft!O11</f>
-        <v>19.323639376190481</v>
+        <v>20.098456209523814</v>
       </c>
       <c r="L9" s="226">
         <f>Overall_Draft!P11</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M9" s="213">
         <f>Overall_Draft!Q11</f>
@@ -26904,11 +26914,11 @@
       </c>
       <c r="N9" s="213">
         <f>Overall_Draft!R11</f>
-        <v>475.35149895714284</v>
+        <v>476.3047423619048</v>
       </c>
       <c r="O9" s="213">
         <f>Overall_Draft!S11</f>
-        <v>10.853153976190475</v>
+        <v>10.449389428571429</v>
       </c>
       <c r="P9" s="226">
         <f>Overall_Draft!T11</f>
@@ -26916,7 +26926,7 @@
       </c>
       <c r="Q9" s="226">
         <f ca="1">Overall_Draft!U11</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R9" s="226">
         <f>Overall_Draft!V11</f>
@@ -26937,11 +26947,11 @@
       </c>
       <c r="W9" s="213">
         <f>Overall_Draft!N43</f>
-        <v>4.6723711904761913</v>
+        <v>4.8369220904761914</v>
       </c>
       <c r="X9" s="214">
         <f>Overall_Draft!O43</f>
-        <v>0.40545908592659802</v>
+        <v>0.41973848599618013</v>
       </c>
       <c r="Y9" s="213">
         <f>Overall_Draft!P43</f>
@@ -26953,11 +26963,11 @@
       </c>
       <c r="AA9" s="213">
         <f>Overall_Draft!R43</f>
-        <v>2.9198205714285717</v>
+        <v>3.1423946190476197</v>
       </c>
       <c r="AB9" s="214">
         <f>Overall_Draft!S43</f>
-        <v>1.92629195924809</v>
+        <v>2.0731306391523501</v>
       </c>
       <c r="AC9" s="213">
         <f>Overall_Draft!T43</f>
@@ -26969,11 +26979,11 @@
       </c>
       <c r="AE9" s="213">
         <f>Overall_Draft!V43</f>
-        <v>1.3182723809523809</v>
+        <v>1.7007692380952382</v>
       </c>
       <c r="AF9" s="214">
         <f>Overall_Draft!W43</f>
-        <v>0.70495849248790421</v>
+        <v>0.90950226636108999</v>
       </c>
       <c r="AG9" s="213">
         <f>Overall_Draft!X43</f>
@@ -27001,11 +27011,11 @@
       </c>
       <c r="AM9" s="213">
         <f>Overall_Draft!AD43</f>
-        <v>3.7617804523809517</v>
+        <v>3.9454020523809517</v>
       </c>
       <c r="AN9" s="214">
         <f>Overall_Draft!AE43</f>
-        <v>0.36101539850105097</v>
+        <v>0.37863743304999531</v>
       </c>
       <c r="AO9" s="213">
         <f>Overall_Draft!AF43</f>
@@ -27037,39 +27047,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="720fc211-b8f9-4216-8e59-f92e385e0bb9">
-      <UserInfo>
-        <DisplayName>Ankit Jain</DisplayName>
-        <AccountId>34</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Poonam</DisplayName>
-        <AccountId>10</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Rishabh Goyal</DisplayName>
-        <AccountId>15</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F060A9DEC12A74CAEC81197F47A267F" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9541e711a3f8d554dd3b47338dc6045a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1c221b64-27b2-4021-9af7-79dcbf083a1e" xmlns:ns3="720fc211-b8f9-4216-8e59-f92e385e0bb9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="098a64c75b1331547a23e680aa36f5f3" ns2:_="" ns3:_="">
     <xsd:import namespace="1c221b64-27b2-4021-9af7-79dcbf083a1e"/>
@@ -27246,32 +27223,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850BD086-9051-4567-AFD1-B7C8873D4F2D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="1c221b64-27b2-4021-9af7-79dcbf083a1e"/>
-    <ds:schemaRef ds:uri="720fc211-b8f9-4216-8e59-f92e385e0bb9"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{037A7D67-D63F-48F5-85CA-5FAB13DF5982}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="720fc211-b8f9-4216-8e59-f92e385e0bb9">
+      <UserInfo>
+        <DisplayName>Ankit Jain</DisplayName>
+        <AccountId>34</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Poonam</DisplayName>
+        <AccountId>10</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Rishabh Goyal</DisplayName>
+        <AccountId>15</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD55F499-65CE-441F-9D64-BBB026E75EFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27288,4 +27273,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{037A7D67-D63F-48F5-85CA-5FAB13DF5982}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850BD086-9051-4567-AFD1-B7C8873D4F2D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="720fc211-b8f9-4216-8e59-f92e385e0bb9"/>
+    <ds:schemaRef ds:uri="1c221b64-27b2-4021-9af7-79dcbf083a1e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>